--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7513,7 +7513,7 @@
         <v>120792882</v>
       </c>
       <c r="B62" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>120792881</v>
       </c>
       <c r="B63" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>120813701</v>
       </c>
       <c r="B64" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169078</v>
+        <v>121169106</v>
       </c>
       <c r="B65" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7841,25 +7841,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768549</v>
+        <v>768519</v>
       </c>
       <c r="R65" t="n">
-        <v>7084957</v>
+        <v>7085101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7918,22 +7918,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7951,10 +7951,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169094</v>
+        <v>121169108</v>
       </c>
       <c r="B66" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7967,42 +7967,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>768518</v>
+        <v>768544</v>
       </c>
       <c r="R66" t="n">
-        <v>7085159</v>
+        <v>7085156</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8037,11 +8029,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8053,22 +8040,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Med lunglav och bohål</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8086,10 +8073,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169095</v>
+        <v>121169107</v>
       </c>
       <c r="B67" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8102,27 +8089,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
@@ -8132,7 +8116,7 @@
         <v>768518</v>
       </c>
       <c r="R67" t="n">
-        <v>7085159</v>
+        <v>7085102</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8167,34 +8151,33 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8212,10 +8195,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169108</v>
+        <v>121169083</v>
       </c>
       <c r="B68" t="n">
-        <v>78598</v>
+        <v>90644</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8228,21 +8211,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8252,10 +8235,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768544</v>
+        <v>768563</v>
       </c>
       <c r="R68" t="n">
-        <v>7085156</v>
+        <v>7084836</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8311,12 +8294,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8337,7 +8320,7 @@
         <v>121169093</v>
       </c>
       <c r="B69" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8460,10 +8443,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169087</v>
+        <v>121169078</v>
       </c>
       <c r="B70" t="n">
-        <v>57364</v>
+        <v>90662</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8472,43 +8455,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768530</v>
+        <v>768549</v>
       </c>
       <c r="R70" t="n">
-        <v>7084802</v>
+        <v>7084957</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8543,11 +8521,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8569,12 +8542,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8592,10 +8565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169103</v>
+        <v>121169084</v>
       </c>
       <c r="B71" t="n">
-        <v>90705</v>
+        <v>57367</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8608,34 +8581,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768584</v>
+        <v>768481</v>
       </c>
       <c r="R71" t="n">
-        <v>7084948</v>
+        <v>7085107</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8672,7 +8650,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8686,22 +8664,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8719,10 +8697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169084</v>
+        <v>121169095</v>
       </c>
       <c r="B72" t="n">
-        <v>57364</v>
+        <v>79682</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8735,39 +8713,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768481</v>
+        <v>768518</v>
       </c>
       <c r="R72" t="n">
-        <v>7085107</v>
+        <v>7085159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8804,7 +8780,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre hackmärken</t>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8813,27 +8789,23 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Silverfura</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8854,7 +8826,7 @@
         <v>121169085</v>
       </c>
       <c r="B73" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8983,10 +8955,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169106</v>
+        <v>121169097</v>
       </c>
       <c r="B74" t="n">
-        <v>78598</v>
+        <v>57720</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8995,38 +8967,46 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768519</v>
+        <v>768571</v>
       </c>
       <c r="R74" t="n">
-        <v>7085101</v>
+        <v>7084796</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9056,11 +9036,21 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9069,26 +9059,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Stående levande</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9105,10 +9075,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169083</v>
+        <v>121169103</v>
       </c>
       <c r="B75" t="n">
-        <v>90634</v>
+        <v>90715</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9121,21 +9091,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9145,10 +9115,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768563</v>
+        <v>768584</v>
       </c>
       <c r="R75" t="n">
-        <v>7084836</v>
+        <v>7084948</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9183,6 +9153,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9204,12 +9179,12 @@
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9227,10 +9202,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169107</v>
+        <v>121169087</v>
       </c>
       <c r="B76" t="n">
-        <v>78598</v>
+        <v>57367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9243,34 +9218,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768518</v>
+        <v>768530</v>
       </c>
       <c r="R76" t="n">
-        <v>7085102</v>
+        <v>7084802</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9305,6 +9285,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9316,22 +9301,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9349,10 +9334,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169097</v>
+        <v>121169094</v>
       </c>
       <c r="B77" t="n">
-        <v>57717</v>
+        <v>57367</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9361,20 +9346,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9387,7 +9372,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9397,10 +9382,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768571</v>
+        <v>768518</v>
       </c>
       <c r="R77" t="n">
-        <v>7084796</v>
+        <v>7085159</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9430,19 +9415,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9453,6 +9433,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Med lunglav och bohål</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula # Med lunglav och bohål</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -8073,10 +8073,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169107</v>
+        <v>121169083</v>
       </c>
       <c r="B67" t="n">
-        <v>78601</v>
+        <v>90644</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8089,21 +8089,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768518</v>
+        <v>768563</v>
       </c>
       <c r="R67" t="n">
-        <v>7085102</v>
+        <v>7084836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8162,22 +8162,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169083</v>
+        <v>121169085</v>
       </c>
       <c r="B68" t="n">
-        <v>90644</v>
+        <v>57367</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8211,34 +8211,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768563</v>
+        <v>768500</v>
       </c>
       <c r="R68" t="n">
-        <v>7084836</v>
+        <v>7085111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8273,6 +8278,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spår vid basen</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8284,22 +8294,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8317,7 +8327,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169093</v>
+        <v>121169095</v>
       </c>
       <c r="B69" t="n">
         <v>79682</v>
@@ -8360,10 +8370,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768523</v>
+        <v>768518</v>
       </c>
       <c r="R69" t="n">
-        <v>7085140</v>
+        <v>7085159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8400,7 +8410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8443,10 +8453,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169078</v>
+        <v>121169103</v>
       </c>
       <c r="B70" t="n">
-        <v>90662</v>
+        <v>90715</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8455,25 +8465,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8483,10 +8493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768549</v>
+        <v>768584</v>
       </c>
       <c r="R70" t="n">
-        <v>7084957</v>
+        <v>7084948</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8521,6 +8531,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8542,12 +8557,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8565,7 +8580,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169084</v>
+        <v>121169087</v>
       </c>
       <c r="B71" t="n">
         <v>57367</v>
@@ -8601,7 +8616,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8610,10 +8625,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768481</v>
+        <v>768530</v>
       </c>
       <c r="R71" t="n">
-        <v>7085107</v>
+        <v>7084802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8650,7 +8665,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre hackmärken</t>
+          <t>Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8664,22 +8679,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8697,10 +8712,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169095</v>
+        <v>121169094</v>
       </c>
       <c r="B72" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8713,26 +8728,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8780,7 +8800,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8789,7 +8809,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8803,9 +8822,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Med lunglav och bohål</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8823,10 +8847,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169085</v>
+        <v>121169107</v>
       </c>
       <c r="B73" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8839,39 +8863,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>768500</v>
+        <v>768518</v>
       </c>
       <c r="R73" t="n">
-        <v>7085111</v>
+        <v>7085102</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8906,11 +8925,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8932,12 +8946,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Basen av silverfuran</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8955,10 +8969,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169097</v>
+        <v>121169093</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>79682</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8967,35 +8981,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9003,10 +9012,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768571</v>
+        <v>768523</v>
       </c>
       <c r="R74" t="n">
-        <v>7084796</v>
+        <v>7085140</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9036,19 +9045,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9057,8 +9061,24 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9075,10 +9095,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169103</v>
+        <v>121169084</v>
       </c>
       <c r="B75" t="n">
-        <v>90715</v>
+        <v>57367</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9091,34 +9111,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768584</v>
+        <v>768481</v>
       </c>
       <c r="R75" t="n">
-        <v>7084948</v>
+        <v>7085107</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9155,7 +9180,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9169,22 +9194,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9202,10 +9227,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169087</v>
+        <v>121169097</v>
       </c>
       <c r="B76" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9214,20 +9239,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9236,21 +9261,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768530</v>
+        <v>768571</v>
       </c>
       <c r="R76" t="n">
-        <v>7084802</v>
+        <v>7084796</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9280,14 +9308,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9298,26 +9331,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9334,10 +9347,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169094</v>
+        <v>121169078</v>
       </c>
       <c r="B77" t="n">
-        <v>57367</v>
+        <v>90662</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9346,46 +9359,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768518</v>
+        <v>768549</v>
       </c>
       <c r="R77" t="n">
-        <v>7085159</v>
+        <v>7084957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9420,11 +9425,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9436,22 +9436,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Med lunglav och bohål</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169106</v>
+        <v>121169084</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,34 +7845,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768519</v>
+        <v>768481</v>
       </c>
       <c r="R65" t="n">
-        <v>7085101</v>
+        <v>7085107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7907,6 +7912,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7928,12 +7938,12 @@
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7954,7 +7964,7 @@
         <v>121169108</v>
       </c>
       <c r="B66" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8073,10 +8083,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169083</v>
+        <v>121169093</v>
       </c>
       <c r="B67" t="n">
-        <v>90644</v>
+        <v>79685</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8089,34 +8099,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768563</v>
+        <v>768523</v>
       </c>
       <c r="R67" t="n">
-        <v>7084836</v>
+        <v>7085140</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8151,33 +8164,34 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8195,10 +8209,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169085</v>
+        <v>121169097</v>
       </c>
       <c r="B68" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8207,20 +8221,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8229,21 +8243,24 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768500</v>
+        <v>768571</v>
       </c>
       <c r="R68" t="n">
-        <v>7085111</v>
+        <v>7084796</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8273,14 +8290,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8291,26 +8313,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>Basen av silverfuran</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8327,10 +8329,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169095</v>
+        <v>121169087</v>
       </c>
       <c r="B69" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8343,37 +8345,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768518</v>
+        <v>768530</v>
       </c>
       <c r="R69" t="n">
-        <v>7085159</v>
+        <v>7084802</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8410,7 +8414,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+          <t>Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8419,23 +8423,27 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8453,10 +8461,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169103</v>
+        <v>121169106</v>
       </c>
       <c r="B70" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8469,21 +8477,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8493,10 +8501,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768584</v>
+        <v>768519</v>
       </c>
       <c r="R70" t="n">
-        <v>7084948</v>
+        <v>7085101</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8531,11 +8539,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8547,22 +8550,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8580,10 +8583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169087</v>
+        <v>121169103</v>
       </c>
       <c r="B71" t="n">
-        <v>57367</v>
+        <v>90727</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8596,39 +8599,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768530</v>
+        <v>768584</v>
       </c>
       <c r="R71" t="n">
-        <v>7084802</v>
+        <v>7084948</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8665,7 +8663,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Både färska och äldre spår</t>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8712,10 +8710,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169094</v>
+        <v>121169107</v>
       </c>
       <c r="B72" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8728,32 +8726,24 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
@@ -8763,7 +8753,7 @@
         <v>768518</v>
       </c>
       <c r="R72" t="n">
-        <v>7085159</v>
+        <v>7085102</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8798,11 +8788,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8814,22 +8799,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Med lunglav och bohål</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8847,10 +8832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169107</v>
+        <v>121169095</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8863,24 +8848,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
@@ -8890,7 +8878,7 @@
         <v>768518</v>
       </c>
       <c r="R73" t="n">
-        <v>7085102</v>
+        <v>7085159</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8925,33 +8913,34 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8969,10 +8958,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169093</v>
+        <v>121169085</v>
       </c>
       <c r="B74" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8985,37 +8974,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768523</v>
+        <v>768500</v>
       </c>
       <c r="R74" t="n">
-        <v>7085140</v>
+        <v>7085111</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9052,7 +9043,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+          <t>Äldre spår vid basen</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9061,23 +9052,27 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9095,7 +9090,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169084</v>
+        <v>121169094</v>
       </c>
       <c r="B75" t="n">
         <v>57367</v>
@@ -9129,21 +9124,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768481</v>
+        <v>768518</v>
       </c>
       <c r="R75" t="n">
-        <v>7085107</v>
+        <v>7085159</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9180,7 +9178,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre hackmärken</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9194,22 +9192,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9227,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169097</v>
+        <v>121169083</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>90656</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9239,46 +9237,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768571</v>
+        <v>768563</v>
       </c>
       <c r="R76" t="n">
-        <v>7084796</v>
+        <v>7084836</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9308,21 +9298,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9331,6 +9311,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Granlåga, mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9350,7 +9350,7 @@
         <v>121169078</v>
       </c>
       <c r="B77" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169084</v>
+        <v>121169083</v>
       </c>
       <c r="B65" t="n">
-        <v>57367</v>
+        <v>90657</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,39 +7845,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768481</v>
+        <v>768563</v>
       </c>
       <c r="R65" t="n">
-        <v>7085107</v>
+        <v>7084836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7912,11 +7907,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7928,22 +7918,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7961,10 +7951,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169108</v>
+        <v>121169087</v>
       </c>
       <c r="B66" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7977,34 +7967,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>768544</v>
+        <v>768530</v>
       </c>
       <c r="R66" t="n">
-        <v>7085156</v>
+        <v>7084802</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8039,6 +8034,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169093</v>
+        <v>121169078</v>
       </c>
       <c r="B67" t="n">
-        <v>79685</v>
+        <v>90675</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8095,41 +8095,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768523</v>
+        <v>768549</v>
       </c>
       <c r="R67" t="n">
-        <v>7085140</v>
+        <v>7084957</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8164,34 +8161,33 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8209,10 +8205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169097</v>
+        <v>121169106</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>78604</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8221,46 +8217,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768571</v>
+        <v>768519</v>
       </c>
       <c r="R68" t="n">
-        <v>7084796</v>
+        <v>7085101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8290,21 +8278,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8313,6 +8291,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Stående levande</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8329,7 +8327,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169087</v>
+        <v>121169094</v>
       </c>
       <c r="B69" t="n">
         <v>57367</v>
@@ -8363,21 +8361,24 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768530</v>
+        <v>768518</v>
       </c>
       <c r="R69" t="n">
-        <v>7084802</v>
+        <v>7085159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8414,7 +8415,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Både färska och äldre spår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8428,22 +8429,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8461,10 +8462,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169106</v>
+        <v>121169085</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8477,34 +8478,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768519</v>
+        <v>768500</v>
       </c>
       <c r="R70" t="n">
-        <v>7085101</v>
+        <v>7085111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8539,6 +8545,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre spår vid basen</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8560,12 +8571,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8583,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169103</v>
+        <v>121169095</v>
       </c>
       <c r="B71" t="n">
-        <v>90727</v>
+        <v>79685</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8599,34 +8610,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768584</v>
+        <v>768518</v>
       </c>
       <c r="R71" t="n">
-        <v>7084948</v>
+        <v>7085159</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8663,7 +8677,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8672,27 +8686,23 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Stående död</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8710,10 +8720,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169107</v>
+        <v>121169084</v>
       </c>
       <c r="B72" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8726,34 +8736,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768518</v>
+        <v>768481</v>
       </c>
       <c r="R72" t="n">
-        <v>7085102</v>
+        <v>7085107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8788,6 +8803,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8809,12 +8829,12 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8832,7 +8852,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169095</v>
+        <v>121169093</v>
       </c>
       <c r="B73" t="n">
         <v>79685</v>
@@ -8875,10 +8895,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>768518</v>
+        <v>768523</v>
       </c>
       <c r="R73" t="n">
-        <v>7085159</v>
+        <v>7085140</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8915,7 +8935,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8958,10 +8978,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169085</v>
+        <v>121169107</v>
       </c>
       <c r="B74" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8974,39 +8994,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768500</v>
+        <v>768518</v>
       </c>
       <c r="R74" t="n">
-        <v>7085111</v>
+        <v>7085102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9041,11 +9056,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9067,12 +9077,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Basen av silverfuran</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9090,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169094</v>
+        <v>121169097</v>
       </c>
       <c r="B75" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9102,20 +9112,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9128,7 +9138,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9138,10 +9148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768518</v>
+        <v>768571</v>
       </c>
       <c r="R75" t="n">
-        <v>7085159</v>
+        <v>7084796</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9171,14 +9181,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9189,26 +9204,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Med lunglav och bohål</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9225,10 +9220,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169083</v>
+        <v>121169108</v>
       </c>
       <c r="B76" t="n">
-        <v>90656</v>
+        <v>78604</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9241,21 +9236,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768563</v>
+        <v>768544</v>
       </c>
       <c r="R76" t="n">
-        <v>7084836</v>
+        <v>7085156</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9324,12 +9319,12 @@
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9347,10 +9342,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169078</v>
+        <v>121169103</v>
       </c>
       <c r="B77" t="n">
-        <v>90674</v>
+        <v>90728</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9359,25 +9354,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9387,10 +9382,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768549</v>
+        <v>768584</v>
       </c>
       <c r="R77" t="n">
-        <v>7084957</v>
+        <v>7084948</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9425,6 +9420,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9446,12 +9446,12 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169083</v>
+        <v>121169106</v>
       </c>
       <c r="B65" t="n">
-        <v>90657</v>
+        <v>78607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768563</v>
+        <v>768519</v>
       </c>
       <c r="R65" t="n">
-        <v>7084836</v>
+        <v>7085101</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7918,22 +7918,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7951,10 +7951,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169087</v>
+        <v>121169083</v>
       </c>
       <c r="B66" t="n">
-        <v>57367</v>
+        <v>90660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7967,39 +7967,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>768530</v>
+        <v>768563</v>
       </c>
       <c r="R66" t="n">
-        <v>7084802</v>
+        <v>7084836</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,11 +8029,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8050,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8083,10 +8073,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169078</v>
+        <v>121169085</v>
       </c>
       <c r="B67" t="n">
-        <v>90675</v>
+        <v>57370</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8095,38 +8085,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768549</v>
+        <v>768500</v>
       </c>
       <c r="R67" t="n">
-        <v>7084957</v>
+        <v>7085111</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8161,6 +8156,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre spår vid basen</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8172,22 +8172,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8205,10 +8205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169106</v>
+        <v>121169095</v>
       </c>
       <c r="B68" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8221,34 +8221,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768519</v>
+        <v>768518</v>
       </c>
       <c r="R68" t="n">
-        <v>7085101</v>
+        <v>7085159</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8283,33 +8286,34 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8327,10 +8331,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169094</v>
+        <v>121169097</v>
       </c>
       <c r="B69" t="n">
-        <v>57367</v>
+        <v>57723</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8339,20 +8343,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8365,7 +8369,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8375,10 +8379,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768518</v>
+        <v>768571</v>
       </c>
       <c r="R69" t="n">
-        <v>7085159</v>
+        <v>7084796</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8408,14 +8412,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8426,26 +8435,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Med lunglav och bohål</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8462,10 +8451,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169085</v>
+        <v>121169103</v>
       </c>
       <c r="B70" t="n">
-        <v>57367</v>
+        <v>90731</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8478,39 +8467,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768500</v>
+        <v>768584</v>
       </c>
       <c r="R70" t="n">
-        <v>7085111</v>
+        <v>7084948</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8547,7 +8531,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre spår vid basen</t>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8561,22 +8545,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Basen av silverfuran</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8594,10 +8578,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169095</v>
+        <v>121169087</v>
       </c>
       <c r="B71" t="n">
-        <v>79685</v>
+        <v>57370</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8610,37 +8594,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768518</v>
+        <v>768530</v>
       </c>
       <c r="R71" t="n">
-        <v>7085159</v>
+        <v>7084802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8677,7 +8663,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+          <t>Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8686,23 +8672,27 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8720,10 +8710,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169084</v>
+        <v>121169094</v>
       </c>
       <c r="B72" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8754,21 +8744,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768481</v>
+        <v>768518</v>
       </c>
       <c r="R72" t="n">
-        <v>7085107</v>
+        <v>7085159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8805,7 +8798,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre hackmärken</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8819,22 +8812,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8855,7 +8848,7 @@
         <v>121169093</v>
       </c>
       <c r="B73" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8978,10 +8971,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169107</v>
+        <v>121169084</v>
       </c>
       <c r="B74" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8994,34 +8987,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768518</v>
+        <v>768481</v>
       </c>
       <c r="R74" t="n">
-        <v>7085102</v>
+        <v>7085107</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9056,6 +9054,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9077,12 +9080,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9100,10 +9103,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169097</v>
+        <v>121169108</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>78607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9112,46 +9115,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768571</v>
+        <v>768544</v>
       </c>
       <c r="R75" t="n">
-        <v>7084796</v>
+        <v>7085156</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9181,21 +9176,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9204,6 +9189,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående levande</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9220,10 +9225,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169108</v>
+        <v>121169078</v>
       </c>
       <c r="B76" t="n">
-        <v>78604</v>
+        <v>90678</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9232,25 +9237,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9260,10 +9265,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768544</v>
+        <v>768549</v>
       </c>
       <c r="R76" t="n">
-        <v>7085156</v>
+        <v>7084957</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9319,12 +9324,12 @@
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9342,10 +9347,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169103</v>
+        <v>121169107</v>
       </c>
       <c r="B77" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9358,21 +9363,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9382,10 +9387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768584</v>
+        <v>768518</v>
       </c>
       <c r="R77" t="n">
-        <v>7084948</v>
+        <v>7085102</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9420,11 +9425,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9436,22 +9436,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169106</v>
+        <v>121169093</v>
       </c>
       <c r="B65" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,34 +7845,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768519</v>
+        <v>768523</v>
       </c>
       <c r="R65" t="n">
-        <v>7085101</v>
+        <v>7085140</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7907,33 +7910,34 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7951,10 +7955,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169083</v>
+        <v>121169087</v>
       </c>
       <c r="B66" t="n">
-        <v>90660</v>
+        <v>57370</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7967,34 +7971,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>768563</v>
+        <v>768530</v>
       </c>
       <c r="R66" t="n">
-        <v>7084836</v>
+        <v>7084802</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8029,6 +8038,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8050,12 +8064,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8073,10 +8087,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169085</v>
+        <v>121169083</v>
       </c>
       <c r="B67" t="n">
-        <v>57370</v>
+        <v>90660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8089,39 +8103,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768500</v>
+        <v>768563</v>
       </c>
       <c r="R67" t="n">
-        <v>7085111</v>
+        <v>7084836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8156,11 +8165,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8172,22 +8176,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Basen av silverfuran</t>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8205,10 +8209,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169095</v>
+        <v>121169108</v>
       </c>
       <c r="B68" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8221,37 +8225,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768518</v>
+        <v>768544</v>
       </c>
       <c r="R68" t="n">
-        <v>7085159</v>
+        <v>7085156</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8286,34 +8287,33 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8331,10 +8331,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169097</v>
+        <v>121169095</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>79688</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8343,35 +8343,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8379,10 +8374,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768571</v>
+        <v>768518</v>
       </c>
       <c r="R69" t="n">
-        <v>7084796</v>
+        <v>7085159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8412,19 +8407,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8433,8 +8423,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8578,10 +8584,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169087</v>
+        <v>121169106</v>
       </c>
       <c r="B71" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8594,39 +8600,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768530</v>
+        <v>768519</v>
       </c>
       <c r="R71" t="n">
-        <v>7084802</v>
+        <v>7085101</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8661,11 +8662,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8677,22 +8673,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8710,7 +8706,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169094</v>
+        <v>121169085</v>
       </c>
       <c r="B72" t="n">
         <v>57370</v>
@@ -8744,24 +8740,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768518</v>
+        <v>768500</v>
       </c>
       <c r="R72" t="n">
-        <v>7085159</v>
+        <v>7085111</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8798,7 +8791,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Äldre spår vid basen</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8812,22 +8805,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Med lunglav och bohål</t>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8845,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169093</v>
+        <v>121169084</v>
       </c>
       <c r="B73" t="n">
-        <v>79688</v>
+        <v>57370</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8861,37 +8854,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>768523</v>
+        <v>768481</v>
       </c>
       <c r="R73" t="n">
-        <v>7085140</v>
+        <v>7085107</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8928,7 +8923,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+          <t>Äldre hackmärken</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8937,23 +8932,27 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8971,10 +8970,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169084</v>
+        <v>121169107</v>
       </c>
       <c r="B74" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8987,39 +8986,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768481</v>
+        <v>768518</v>
       </c>
       <c r="R74" t="n">
-        <v>7085107</v>
+        <v>7085102</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9054,11 +9048,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9080,12 +9069,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9103,10 +9092,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169108</v>
+        <v>121169097</v>
       </c>
       <c r="B75" t="n">
-        <v>78607</v>
+        <v>57723</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9115,38 +9104,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768544</v>
+        <v>768571</v>
       </c>
       <c r="R75" t="n">
-        <v>7085156</v>
+        <v>7084796</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9176,11 +9173,21 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9189,26 +9196,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Stående levande</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående levande</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9225,10 +9212,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169078</v>
+        <v>121169094</v>
       </c>
       <c r="B76" t="n">
-        <v>90678</v>
+        <v>57370</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9237,38 +9224,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768549</v>
+        <v>768518</v>
       </c>
       <c r="R76" t="n">
-        <v>7084957</v>
+        <v>7085159</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9303,6 +9298,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9314,22 +9314,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169107</v>
+        <v>121169078</v>
       </c>
       <c r="B77" t="n">
-        <v>78607</v>
+        <v>90678</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9359,25 +9359,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768518</v>
+        <v>768549</v>
       </c>
       <c r="R77" t="n">
-        <v>7085102</v>
+        <v>7084957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9436,22 +9436,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -7829,10 +7829,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169093</v>
+        <v>121169083</v>
       </c>
       <c r="B65" t="n">
-        <v>79688</v>
+        <v>90666</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,37 +7845,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768523</v>
+        <v>768563</v>
       </c>
       <c r="R65" t="n">
-        <v>7085140</v>
+        <v>7084836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7910,34 +7907,33 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7955,10 +7951,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169087</v>
+        <v>121169094</v>
       </c>
       <c r="B66" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7989,21 +7985,24 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>768530</v>
+        <v>768518</v>
       </c>
       <c r="R66" t="n">
-        <v>7084802</v>
+        <v>7085159</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8040,7 +8039,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Både färska och äldre spår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8054,22 +8053,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8087,10 +8086,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169083</v>
+        <v>121169095</v>
       </c>
       <c r="B67" t="n">
-        <v>90660</v>
+        <v>79689</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8103,34 +8102,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768563</v>
+        <v>768518</v>
       </c>
       <c r="R67" t="n">
-        <v>7084836</v>
+        <v>7085159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8165,33 +8167,34 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8209,10 +8212,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169108</v>
+        <v>121169087</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8225,34 +8228,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768544</v>
+        <v>768530</v>
       </c>
       <c r="R68" t="n">
-        <v>7085156</v>
+        <v>7084802</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8287,6 +8295,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8308,12 +8321,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8331,10 +8344,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169095</v>
+        <v>121169107</v>
       </c>
       <c r="B69" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8347,27 +8360,24 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
@@ -8377,7 +8387,7 @@
         <v>768518</v>
       </c>
       <c r="R69" t="n">
-        <v>7085159</v>
+        <v>7085102</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8412,34 +8422,33 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8457,10 +8466,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169103</v>
+        <v>121169108</v>
       </c>
       <c r="B70" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8473,21 +8482,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8497,10 +8506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768584</v>
+        <v>768544</v>
       </c>
       <c r="R70" t="n">
-        <v>7084948</v>
+        <v>7085156</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8535,11 +8544,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8561,12 +8565,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8584,10 +8588,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169106</v>
+        <v>121169084</v>
       </c>
       <c r="B71" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8600,34 +8604,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768519</v>
+        <v>768481</v>
       </c>
       <c r="R71" t="n">
-        <v>7085101</v>
+        <v>7085107</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8662,6 +8671,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8683,12 +8697,12 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8706,10 +8720,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169085</v>
+        <v>121169097</v>
       </c>
       <c r="B72" t="n">
-        <v>57370</v>
+        <v>57724</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8718,20 +8732,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8740,21 +8754,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768500</v>
+        <v>768571</v>
       </c>
       <c r="R72" t="n">
-        <v>7085111</v>
+        <v>7084796</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8784,14 +8801,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8802,26 +8824,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Basen av silverfuran</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8838,10 +8840,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169084</v>
+        <v>121169106</v>
       </c>
       <c r="B73" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8854,39 +8856,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>768481</v>
+        <v>768519</v>
       </c>
       <c r="R73" t="n">
-        <v>7085107</v>
+        <v>7085101</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8921,11 +8918,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8947,12 +8939,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8970,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169107</v>
+        <v>121169078</v>
       </c>
       <c r="B74" t="n">
-        <v>78607</v>
+        <v>90684</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8982,25 +8974,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9010,10 +9002,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768518</v>
+        <v>768549</v>
       </c>
       <c r="R74" t="n">
-        <v>7085102</v>
+        <v>7084957</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9059,22 +9051,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9092,10 +9084,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169097</v>
+        <v>121169103</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>90737</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9104,46 +9096,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768571</v>
+        <v>768584</v>
       </c>
       <c r="R75" t="n">
-        <v>7084796</v>
+        <v>7084948</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9173,19 +9157,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:15</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9196,6 +9175,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9212,10 +9211,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169094</v>
+        <v>121169093</v>
       </c>
       <c r="B76" t="n">
-        <v>57370</v>
+        <v>79689</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9228,31 +9227,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9260,10 +9254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768518</v>
+        <v>768523</v>
       </c>
       <c r="R76" t="n">
-        <v>7085159</v>
+        <v>7085140</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9300,7 +9294,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9309,6 +9303,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9322,14 +9317,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Med lunglav och bohål</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9347,10 +9337,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169078</v>
+        <v>121169085</v>
       </c>
       <c r="B77" t="n">
-        <v>90678</v>
+        <v>57371</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9359,38 +9349,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768549</v>
+        <v>768500</v>
       </c>
       <c r="R77" t="n">
-        <v>7084957</v>
+        <v>7085111</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9425,6 +9420,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre spår vid basen</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9436,22 +9436,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9467,6 +9467,120 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121595937</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>768640</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7085029</v>
+      </c>
+      <c r="S78" t="n">
+        <v>50</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9472,7 +9472,7 @@
         <v>121595937</v>
       </c>
       <c r="B78" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9581,6 +9581,528 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122951641</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stubbmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>768458</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7084852</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122951645</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>768634</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7084758</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122951643</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>768541</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7084820</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122951724</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>768640</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7085029</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122951644</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78800</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>185</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>768631</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7084761</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951641</v>
+        <v>122951645</v>
       </c>
       <c r="B79" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,38 +9595,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768458</v>
+        <v>768634</v>
       </c>
       <c r="R79" t="n">
-        <v>7084852</v>
+        <v>7084758</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951645</v>
+        <v>122951641</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,38 +9697,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768634</v>
+        <v>768458</v>
       </c>
       <c r="R80" t="n">
-        <v>7084758</v>
+        <v>7084852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9787,10 +9787,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>57848</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9799,41 +9799,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R81" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9889,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951724</v>
+        <v>122951644</v>
       </c>
       <c r="B82" t="n">
-        <v>57848</v>
+        <v>78800</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9901,53 +9913,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768640</v>
+        <v>768631</v>
       </c>
       <c r="R82" t="n">
-        <v>7085029</v>
+        <v>7084761</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951644</v>
+        <v>122951643</v>
       </c>
       <c r="B83" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10019,21 +10019,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768631</v>
+        <v>768541</v>
       </c>
       <c r="R83" t="n">
-        <v>7084761</v>
+        <v>7084820</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951645</v>
+        <v>122951644</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>78800</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9599,21 +9599,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768634</v>
+        <v>768631</v>
       </c>
       <c r="R79" t="n">
-        <v>7084758</v>
+        <v>7084761</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951641</v>
+        <v>122951724</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>57848</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9701,37 +9701,49 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768458</v>
+        <v>768640</v>
       </c>
       <c r="R80" t="n">
-        <v>7084852</v>
+        <v>7085029</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9787,10 +9799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951724</v>
+        <v>122951641</v>
       </c>
       <c r="B81" t="n">
-        <v>57848</v>
+        <v>78792</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9803,49 +9815,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768640</v>
+        <v>768458</v>
       </c>
       <c r="R81" t="n">
-        <v>7085029</v>
+        <v>7084852</v>
       </c>
       <c r="S81" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951644</v>
+        <v>122951645</v>
       </c>
       <c r="B82" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9917,21 +9917,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768631</v>
+        <v>768634</v>
       </c>
       <c r="R82" t="n">
-        <v>7084761</v>
+        <v>7084758</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951644</v>
+        <v>122951643</v>
       </c>
       <c r="B79" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9599,21 +9599,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768631</v>
+        <v>768541</v>
       </c>
       <c r="R79" t="n">
-        <v>7084761</v>
+        <v>7084820</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951724</v>
+        <v>122951645</v>
       </c>
       <c r="B80" t="n">
-        <v>57848</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,53 +9697,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768640</v>
+        <v>768634</v>
       </c>
       <c r="R80" t="n">
-        <v>7085029</v>
+        <v>7084758</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9802,7 +9790,7 @@
         <v>122951641</v>
       </c>
       <c r="B81" t="n">
-        <v>78792</v>
+        <v>78790</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9901,10 +9889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951645</v>
+        <v>122951644</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>78798</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9917,21 +9905,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9941,10 +9929,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768634</v>
+        <v>768631</v>
       </c>
       <c r="R82" t="n">
-        <v>7084758</v>
+        <v>7084761</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10003,10 +9991,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B83" t="n">
-        <v>78766</v>
+        <v>57848</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,41 +10003,53 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R83" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9787,10 +9787,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951641</v>
+        <v>122951724</v>
       </c>
       <c r="B81" t="n">
-        <v>78790</v>
+        <v>57848</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9803,37 +9803,49 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768458</v>
+        <v>768640</v>
       </c>
       <c r="R81" t="n">
-        <v>7084852</v>
+        <v>7085029</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9889,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951644</v>
+        <v>122951641</v>
       </c>
       <c r="B82" t="n">
-        <v>78798</v>
+        <v>78790</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9901,38 +9913,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768631</v>
+        <v>768458</v>
       </c>
       <c r="R82" t="n">
-        <v>7084761</v>
+        <v>7084852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9991,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951724</v>
+        <v>122951644</v>
       </c>
       <c r="B83" t="n">
-        <v>57848</v>
+        <v>78798</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10003,53 +10015,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768640</v>
+        <v>768631</v>
       </c>
       <c r="R83" t="n">
-        <v>7085029</v>
+        <v>7084761</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951645</v>
+        <v>122951641</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,38 +9697,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768634</v>
+        <v>768458</v>
       </c>
       <c r="R80" t="n">
-        <v>7084758</v>
+        <v>7084852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951641</v>
+        <v>122951645</v>
       </c>
       <c r="B82" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9913,38 +9913,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768458</v>
+        <v>768634</v>
       </c>
       <c r="R82" t="n">
-        <v>7084852</v>
+        <v>7084758</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951641</v>
+        <v>122951645</v>
       </c>
       <c r="B80" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,38 +9697,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768458</v>
+        <v>768634</v>
       </c>
       <c r="R80" t="n">
-        <v>7084852</v>
+        <v>7084758</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9787,10 +9787,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951724</v>
+        <v>122951644</v>
       </c>
       <c r="B81" t="n">
-        <v>57848</v>
+        <v>78798</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9799,53 +9799,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768640</v>
+        <v>768631</v>
       </c>
       <c r="R81" t="n">
-        <v>7085029</v>
+        <v>7084761</v>
       </c>
       <c r="S81" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9901,10 +9889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951645</v>
+        <v>122951641</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9913,38 +9901,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768634</v>
+        <v>768458</v>
       </c>
       <c r="R82" t="n">
-        <v>7084758</v>
+        <v>7084852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10003,10 +9991,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951644</v>
+        <v>122951724</v>
       </c>
       <c r="B83" t="n">
-        <v>78798</v>
+        <v>57848</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,41 +10003,53 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768631</v>
+        <v>768640</v>
       </c>
       <c r="R83" t="n">
-        <v>7084761</v>
+        <v>7085029</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>57851</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,41 +9595,53 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R79" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9685,10 +9697,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951645</v>
+        <v>122951644</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>78801</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9701,21 +9713,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9725,10 +9737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768634</v>
+        <v>768631</v>
       </c>
       <c r="R80" t="n">
-        <v>7084758</v>
+        <v>7084761</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9787,10 +9799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951644</v>
+        <v>122951645</v>
       </c>
       <c r="B81" t="n">
-        <v>78798</v>
+        <v>78769</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9803,21 +9815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9827,10 +9839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768631</v>
+        <v>768634</v>
       </c>
       <c r="R81" t="n">
-        <v>7084761</v>
+        <v>7084758</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9892,7 +9904,7 @@
         <v>122951641</v>
       </c>
       <c r="B82" t="n">
-        <v>78790</v>
+        <v>78793</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9991,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951724</v>
+        <v>122951643</v>
       </c>
       <c r="B83" t="n">
-        <v>57848</v>
+        <v>78769</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10003,53 +10015,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768640</v>
+        <v>768541</v>
       </c>
       <c r="R83" t="n">
-        <v>7085029</v>
+        <v>7084820</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951724</v>
+        <v>122951644</v>
       </c>
       <c r="B79" t="n">
-        <v>57851</v>
+        <v>78803</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,53 +9595,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768640</v>
+        <v>768631</v>
       </c>
       <c r="R79" t="n">
-        <v>7085029</v>
+        <v>7084761</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9697,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951644</v>
+        <v>122951724</v>
       </c>
       <c r="B80" t="n">
-        <v>78801</v>
+        <v>57851</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9709,41 +9697,53 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768631</v>
+        <v>768640</v>
       </c>
       <c r="R80" t="n">
-        <v>7084761</v>
+        <v>7085029</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>122951645</v>
       </c>
       <c r="B81" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951641</v>
+        <v>122951643</v>
       </c>
       <c r="B82" t="n">
-        <v>78793</v>
+        <v>78771</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9913,38 +9913,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768458</v>
+        <v>768541</v>
       </c>
       <c r="R82" t="n">
-        <v>7084852</v>
+        <v>7084820</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951643</v>
+        <v>122951641</v>
       </c>
       <c r="B83" t="n">
-        <v>78769</v>
+        <v>78795</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,38 +10015,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768541</v>
+        <v>768458</v>
       </c>
       <c r="R83" t="n">
-        <v>7084820</v>
+        <v>7084852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951644</v>
+        <v>122951641</v>
       </c>
       <c r="B79" t="n">
-        <v>78803</v>
+        <v>78796</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,38 +9595,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768631</v>
+        <v>768458</v>
       </c>
       <c r="R79" t="n">
-        <v>7084761</v>
+        <v>7084852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951724</v>
+        <v>122951643</v>
       </c>
       <c r="B80" t="n">
-        <v>57851</v>
+        <v>78772</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,53 +9697,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768640</v>
+        <v>768541</v>
       </c>
       <c r="R80" t="n">
-        <v>7085029</v>
+        <v>7084820</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9802,7 +9790,7 @@
         <v>122951645</v>
       </c>
       <c r="B81" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9901,10 +9889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B82" t="n">
-        <v>78771</v>
+        <v>57851</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9913,41 +9901,53 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R82" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951641</v>
+        <v>122951644</v>
       </c>
       <c r="B83" t="n">
-        <v>78795</v>
+        <v>78804</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,38 +10015,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768458</v>
+        <v>768631</v>
       </c>
       <c r="R83" t="n">
-        <v>7084852</v>
+        <v>7084761</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951641</v>
+        <v>122951643</v>
       </c>
       <c r="B79" t="n">
-        <v>78796</v>
+        <v>78775</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,38 +9595,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768458</v>
+        <v>768541</v>
       </c>
       <c r="R79" t="n">
-        <v>7084852</v>
+        <v>7084820</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B80" t="n">
-        <v>78772</v>
+        <v>57851</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,41 +9697,53 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R80" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9787,10 +9799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951645</v>
+        <v>122951644</v>
       </c>
       <c r="B81" t="n">
-        <v>78772</v>
+        <v>78807</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9803,21 +9815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9827,10 +9839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768634</v>
+        <v>768631</v>
       </c>
       <c r="R81" t="n">
-        <v>7084758</v>
+        <v>7084761</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9889,10 +9901,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951724</v>
+        <v>122951641</v>
       </c>
       <c r="B82" t="n">
-        <v>57851</v>
+        <v>78799</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9905,49 +9917,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768640</v>
+        <v>768458</v>
       </c>
       <c r="R82" t="n">
-        <v>7085029</v>
+        <v>7084852</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951644</v>
+        <v>122951645</v>
       </c>
       <c r="B83" t="n">
-        <v>78804</v>
+        <v>78775</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10019,21 +10019,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768631</v>
+        <v>768634</v>
       </c>
       <c r="R83" t="n">
-        <v>7084761</v>
+        <v>7084758</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -9583,10 +9583,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951643</v>
+        <v>122951644</v>
       </c>
       <c r="B79" t="n">
-        <v>78775</v>
+        <v>78813</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9599,21 +9599,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768541</v>
+        <v>768631</v>
       </c>
       <c r="R79" t="n">
-        <v>7084820</v>
+        <v>7084761</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951724</v>
+        <v>122951641</v>
       </c>
       <c r="B80" t="n">
-        <v>57851</v>
+        <v>78805</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9701,49 +9701,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768640</v>
+        <v>768458</v>
       </c>
       <c r="R80" t="n">
-        <v>7085029</v>
+        <v>7084852</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9799,10 +9787,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951644</v>
+        <v>122951645</v>
       </c>
       <c r="B81" t="n">
-        <v>78807</v>
+        <v>78781</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9815,21 +9803,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9839,10 +9827,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768631</v>
+        <v>768634</v>
       </c>
       <c r="R81" t="n">
-        <v>7084761</v>
+        <v>7084758</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9901,10 +9889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951641</v>
+        <v>122951643</v>
       </c>
       <c r="B82" t="n">
-        <v>78799</v>
+        <v>78781</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9913,38 +9901,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768458</v>
+        <v>768541</v>
       </c>
       <c r="R82" t="n">
-        <v>7084852</v>
+        <v>7084820</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10003,10 +9991,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951645</v>
+        <v>122951724</v>
       </c>
       <c r="B83" t="n">
-        <v>78775</v>
+        <v>57857</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,41 +10003,53 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768634</v>
+        <v>768640</v>
       </c>
       <c r="R83" t="n">
-        <v>7084758</v>
+        <v>7085029</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10105,10 +10105,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622737</v>
+        <v>123622667</v>
       </c>
       <c r="B84" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10121,21 +10121,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10145,10 +10145,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768519</v>
+        <v>768557</v>
       </c>
       <c r="R84" t="n">
-        <v>7085133</v>
+        <v>7085109</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10201,11 +10201,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10222,10 +10217,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622729</v>
+        <v>123622726</v>
       </c>
       <c r="B85" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10238,39 +10233,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768416</v>
+        <v>768378</v>
       </c>
       <c r="R85" t="n">
-        <v>7085204</v>
+        <v>7085228</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10315,11 +10305,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10328,11 +10313,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10349,10 +10329,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622725</v>
+        <v>123622718</v>
       </c>
       <c r="B86" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10385,14 +10365,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768375</v>
+        <v>768450</v>
       </c>
       <c r="R86" t="n">
-        <v>7085205</v>
+        <v>7085128</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10461,10 +10441,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622731</v>
+        <v>123622666</v>
       </c>
       <c r="B87" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10473,25 +10453,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10501,10 +10481,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768463</v>
+        <v>768567</v>
       </c>
       <c r="R87" t="n">
-        <v>7085154</v>
+        <v>7085161</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10573,10 +10553,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622726</v>
+        <v>123622727</v>
       </c>
       <c r="B88" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10613,10 +10593,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768378</v>
+        <v>768402</v>
       </c>
       <c r="R88" t="n">
-        <v>7085228</v>
+        <v>7085218</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10685,10 +10665,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622717</v>
+        <v>123622723</v>
       </c>
       <c r="B89" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10701,21 +10681,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10725,10 +10705,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768463</v>
+        <v>768385</v>
       </c>
       <c r="R89" t="n">
-        <v>7085126</v>
+        <v>7085111</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10781,11 +10761,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10802,10 +10777,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622701</v>
+        <v>123622665</v>
       </c>
       <c r="B90" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10838,14 +10813,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768642</v>
+        <v>768559</v>
       </c>
       <c r="R90" t="n">
-        <v>7084688</v>
+        <v>7085175</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10914,10 +10889,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622715</v>
+        <v>123622710</v>
       </c>
       <c r="B91" t="n">
-        <v>78807</v>
+        <v>57487</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,34 +10905,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768491</v>
+        <v>768591</v>
       </c>
       <c r="R91" t="n">
-        <v>7085072</v>
+        <v>7084882</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11002,6 +10982,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -11010,6 +10995,11 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11026,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622711</v>
+        <v>123622713</v>
       </c>
       <c r="B92" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11062,14 +11052,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768579</v>
+        <v>768497</v>
       </c>
       <c r="R92" t="n">
-        <v>7084911</v>
+        <v>7085012</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11138,10 +11128,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622712</v>
+        <v>123622731</v>
       </c>
       <c r="B93" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11174,14 +11164,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768522</v>
+        <v>768463</v>
       </c>
       <c r="R93" t="n">
-        <v>7084946</v>
+        <v>7085154</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11250,10 +11240,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622727</v>
+        <v>123622732</v>
       </c>
       <c r="B94" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11290,10 +11280,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768402</v>
+        <v>768481</v>
       </c>
       <c r="R94" t="n">
-        <v>7085218</v>
+        <v>7085143</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11362,10 +11352,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622702</v>
+        <v>123622735</v>
       </c>
       <c r="B95" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11398,14 +11388,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768615</v>
+        <v>768515</v>
       </c>
       <c r="R95" t="n">
-        <v>7084711</v>
+        <v>7085140</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11474,10 +11464,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622670</v>
+        <v>123622733</v>
       </c>
       <c r="B96" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11486,38 +11476,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768634</v>
+        <v>768511</v>
       </c>
       <c r="R96" t="n">
-        <v>7084898</v>
+        <v>7085142</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11586,10 +11576,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622713</v>
+        <v>123622725</v>
       </c>
       <c r="B97" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11622,14 +11612,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768497</v>
+        <v>768375</v>
       </c>
       <c r="R97" t="n">
-        <v>7085012</v>
+        <v>7085205</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11698,10 +11688,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622706</v>
+        <v>123622702</v>
       </c>
       <c r="B98" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11738,10 +11728,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768635</v>
+        <v>768615</v>
       </c>
       <c r="R98" t="n">
-        <v>7084793</v>
+        <v>7084711</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11810,10 +11800,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622733</v>
+        <v>123622737</v>
       </c>
       <c r="B99" t="n">
-        <v>78799</v>
+        <v>79862</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11822,25 +11812,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11850,10 +11840,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768511</v>
+        <v>768519</v>
       </c>
       <c r="R99" t="n">
-        <v>7085142</v>
+        <v>7085133</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11906,6 +11896,11 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11922,10 +11917,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622730</v>
+        <v>123622709</v>
       </c>
       <c r="B100" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11958,14 +11953,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768457</v>
+        <v>768616</v>
       </c>
       <c r="R100" t="n">
-        <v>7085185</v>
+        <v>7084853</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12034,10 +12029,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622723</v>
+        <v>123622670</v>
       </c>
       <c r="B101" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12070,14 +12065,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768385</v>
+        <v>768634</v>
       </c>
       <c r="R101" t="n">
-        <v>7085111</v>
+        <v>7084898</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12146,10 +12141,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622666</v>
+        <v>123622717</v>
       </c>
       <c r="B102" t="n">
-        <v>78799</v>
+        <v>79862</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12158,38 +12153,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768567</v>
+        <v>768463</v>
       </c>
       <c r="R102" t="n">
-        <v>7085161</v>
+        <v>7085126</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12242,6 +12237,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12258,10 +12258,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622710</v>
+        <v>123622706</v>
       </c>
       <c r="B103" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12274,39 +12274,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768591</v>
+        <v>768635</v>
       </c>
       <c r="R103" t="n">
-        <v>7084882</v>
+        <v>7084793</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12351,11 +12346,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12364,11 +12354,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12385,10 +12370,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622720</v>
+        <v>123622719</v>
       </c>
       <c r="B104" t="n">
-        <v>78775</v>
+        <v>79317</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12401,21 +12386,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12425,7 +12410,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768441</v>
+        <v>768453</v>
       </c>
       <c r="R104" t="n">
         <v>7085131</v>
@@ -12481,6 +12466,11 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12497,10 +12487,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622665</v>
+        <v>123622701</v>
       </c>
       <c r="B105" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12533,14 +12523,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768559</v>
+        <v>768642</v>
       </c>
       <c r="R105" t="n">
-        <v>7085175</v>
+        <v>7084688</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12609,10 +12599,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622714</v>
+        <v>123622711</v>
       </c>
       <c r="B106" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12645,14 +12635,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768493</v>
+        <v>768579</v>
       </c>
       <c r="R106" t="n">
-        <v>7085068</v>
+        <v>7084911</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12721,10 +12711,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622704</v>
+        <v>123622716</v>
       </c>
       <c r="B107" t="n">
-        <v>56683</v>
+        <v>79317</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12737,51 +12727,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>1352</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768617</v>
+        <v>768463</v>
       </c>
       <c r="R107" t="n">
-        <v>7084779</v>
+        <v>7085126</v>
       </c>
       <c r="S107" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12831,6 +12807,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12847,10 +12828,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622718</v>
+        <v>123622720</v>
       </c>
       <c r="B108" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12887,10 +12868,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768450</v>
+        <v>768441</v>
       </c>
       <c r="R108" t="n">
-        <v>7085128</v>
+        <v>7085131</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12959,10 +12940,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622703</v>
+        <v>123622704</v>
       </c>
       <c r="B109" t="n">
-        <v>78775</v>
+        <v>56689</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12975,37 +12956,51 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768619</v>
+        <v>768617</v>
       </c>
       <c r="R109" t="n">
-        <v>7084757</v>
+        <v>7084779</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13071,10 +13066,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622732</v>
+        <v>123622703</v>
       </c>
       <c r="B110" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13107,14 +13102,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768481</v>
+        <v>768619</v>
       </c>
       <c r="R110" t="n">
-        <v>7085143</v>
+        <v>7084757</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13183,10 +13178,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622667</v>
+        <v>123622712</v>
       </c>
       <c r="B111" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13219,14 +13214,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768557</v>
+        <v>768522</v>
       </c>
       <c r="R111" t="n">
-        <v>7085109</v>
+        <v>7084946</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13295,10 +13290,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622716</v>
+        <v>123622715</v>
       </c>
       <c r="B112" t="n">
-        <v>79311</v>
+        <v>78813</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13311,21 +13306,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1352</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13335,10 +13330,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768463</v>
+        <v>768491</v>
       </c>
       <c r="R112" t="n">
-        <v>7085126</v>
+        <v>7085072</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13391,11 +13386,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13412,10 +13402,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622709</v>
+        <v>123622705</v>
       </c>
       <c r="B113" t="n">
-        <v>78775</v>
+        <v>90948</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13424,25 +13414,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13452,10 +13442,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768616</v>
+        <v>768635</v>
       </c>
       <c r="R113" t="n">
-        <v>7084853</v>
+        <v>7084792</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13508,6 +13498,11 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13524,10 +13519,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622719</v>
+        <v>123622729</v>
       </c>
       <c r="B114" t="n">
-        <v>79311</v>
+        <v>57487</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13540,34 +13535,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1352</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768453</v>
+        <v>768416</v>
       </c>
       <c r="R114" t="n">
-        <v>7085131</v>
+        <v>7085204</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13612,6 +13612,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13623,7 +13628,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>döda granar</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13641,10 +13646,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622705</v>
+        <v>123622730</v>
       </c>
       <c r="B115" t="n">
-        <v>90931</v>
+        <v>78781</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13653,38 +13658,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768635</v>
+        <v>768457</v>
       </c>
       <c r="R115" t="n">
-        <v>7084792</v>
+        <v>7085185</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13737,11 +13742,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13758,10 +13758,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123622735</v>
+        <v>123622714</v>
       </c>
       <c r="B116" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13794,14 +13794,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>768515</v>
+        <v>768493</v>
       </c>
       <c r="R116" t="n">
-        <v>7085140</v>
+        <v>7085068</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -12940,10 +12940,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622704</v>
+        <v>123622703</v>
       </c>
       <c r="B109" t="n">
-        <v>56689</v>
+        <v>78781</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12956,51 +12956,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768617</v>
+        <v>768619</v>
       </c>
       <c r="R109" t="n">
-        <v>7084779</v>
+        <v>7084757</v>
       </c>
       <c r="S109" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13066,7 +13052,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622703</v>
+        <v>123622712</v>
       </c>
       <c r="B110" t="n">
         <v>78781</v>
@@ -13102,14 +13088,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768619</v>
+        <v>768522</v>
       </c>
       <c r="R110" t="n">
-        <v>7084757</v>
+        <v>7084946</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13178,10 +13164,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622712</v>
+        <v>123622704</v>
       </c>
       <c r="B111" t="n">
-        <v>78781</v>
+        <v>56689</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13194,37 +13180,51 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768522</v>
+        <v>768617</v>
       </c>
       <c r="R111" t="n">
-        <v>7084946</v>
+        <v>7084779</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -11128,7 +11128,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622731</v>
+        <v>123622732</v>
       </c>
       <c r="B93" t="n">
         <v>78781</v>
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768463</v>
+        <v>768481</v>
       </c>
       <c r="R93" t="n">
-        <v>7085154</v>
+        <v>7085143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11240,7 +11240,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622732</v>
+        <v>123622735</v>
       </c>
       <c r="B94" t="n">
         <v>78781</v>
@@ -11280,10 +11280,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768481</v>
+        <v>768515</v>
       </c>
       <c r="R94" t="n">
-        <v>7085143</v>
+        <v>7085140</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622735</v>
+        <v>123622731</v>
       </c>
       <c r="B95" t="n">
         <v>78781</v>
@@ -11392,10 +11392,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768515</v>
+        <v>768463</v>
       </c>
       <c r="R95" t="n">
-        <v>7085140</v>
+        <v>7085154</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12940,10 +12940,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622703</v>
+        <v>123622704</v>
       </c>
       <c r="B109" t="n">
-        <v>78781</v>
+        <v>56689</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12956,37 +12956,51 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768619</v>
+        <v>768617</v>
       </c>
       <c r="R109" t="n">
-        <v>7084757</v>
+        <v>7084779</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13052,7 +13066,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622712</v>
+        <v>123622703</v>
       </c>
       <c r="B110" t="n">
         <v>78781</v>
@@ -13088,14 +13102,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768522</v>
+        <v>768619</v>
       </c>
       <c r="R110" t="n">
-        <v>7084946</v>
+        <v>7084757</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13164,10 +13178,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622704</v>
+        <v>123622712</v>
       </c>
       <c r="B111" t="n">
-        <v>56689</v>
+        <v>78781</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13180,51 +13194,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768617</v>
+        <v>768522</v>
       </c>
       <c r="R111" t="n">
-        <v>7084779</v>
+        <v>7084946</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -12487,10 +12487,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622701</v>
+        <v>123622716</v>
       </c>
       <c r="B105" t="n">
-        <v>78781</v>
+        <v>79317</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12503,34 +12503,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768642</v>
+        <v>768463</v>
       </c>
       <c r="R105" t="n">
-        <v>7084688</v>
+        <v>7085126</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12583,6 +12583,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12599,7 +12604,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622711</v>
+        <v>123622701</v>
       </c>
       <c r="B106" t="n">
         <v>78781</v>
@@ -12639,10 +12644,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768579</v>
+        <v>768642</v>
       </c>
       <c r="R106" t="n">
-        <v>7084911</v>
+        <v>7084688</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12711,10 +12716,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622716</v>
+        <v>123622711</v>
       </c>
       <c r="B107" t="n">
-        <v>79317</v>
+        <v>78781</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12727,34 +12732,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768463</v>
+        <v>768579</v>
       </c>
       <c r="R107" t="n">
-        <v>7085126</v>
+        <v>7084911</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12807,11 +12812,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10105,10 +10105,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622667</v>
+        <v>123622709</v>
       </c>
       <c r="B84" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10141,14 +10141,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768557</v>
+        <v>768616</v>
       </c>
       <c r="R84" t="n">
-        <v>7085109</v>
+        <v>7084853</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10217,10 +10217,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622726</v>
+        <v>123622706</v>
       </c>
       <c r="B85" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10253,14 +10253,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768378</v>
+        <v>768635</v>
       </c>
       <c r="R85" t="n">
-        <v>7085228</v>
+        <v>7084793</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10329,10 +10329,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622718</v>
+        <v>123622702</v>
       </c>
       <c r="B86" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10365,14 +10365,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768450</v>
+        <v>768615</v>
       </c>
       <c r="R86" t="n">
-        <v>7085128</v>
+        <v>7084711</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622666</v>
+        <v>123622711</v>
       </c>
       <c r="B87" t="n">
-        <v>78805</v>
+        <v>78786</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10453,38 +10453,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768567</v>
+        <v>768579</v>
       </c>
       <c r="R87" t="n">
-        <v>7085161</v>
+        <v>7084911</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622727</v>
+        <v>123622705</v>
       </c>
       <c r="B88" t="n">
-        <v>78781</v>
+        <v>90953</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10565,38 +10565,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768402</v>
+        <v>768635</v>
       </c>
       <c r="R88" t="n">
-        <v>7085218</v>
+        <v>7084792</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10649,6 +10649,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10665,10 +10670,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622723</v>
+        <v>123622730</v>
       </c>
       <c r="B89" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10701,14 +10706,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768385</v>
+        <v>768457</v>
       </c>
       <c r="R89" t="n">
-        <v>7085111</v>
+        <v>7085185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10777,10 +10782,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622665</v>
+        <v>123622704</v>
       </c>
       <c r="B90" t="n">
-        <v>78781</v>
+        <v>56692</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10793,37 +10798,51 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768559</v>
+        <v>768617</v>
       </c>
       <c r="R90" t="n">
-        <v>7085175</v>
+        <v>7084779</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10889,10 +10908,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622710</v>
+        <v>123622720</v>
       </c>
       <c r="B91" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10905,39 +10924,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768591</v>
+        <v>768441</v>
       </c>
       <c r="R91" t="n">
-        <v>7084882</v>
+        <v>7085131</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10982,11 +10996,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10995,11 +11004,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11016,10 +11020,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622713</v>
+        <v>123622715</v>
       </c>
       <c r="B92" t="n">
-        <v>78781</v>
+        <v>78818</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11032,21 +11036,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11056,10 +11060,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768497</v>
+        <v>768491</v>
       </c>
       <c r="R92" t="n">
-        <v>7085012</v>
+        <v>7085072</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11128,10 +11132,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622732</v>
+        <v>123622719</v>
       </c>
       <c r="B93" t="n">
-        <v>78781</v>
+        <v>79322</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11144,34 +11148,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768481</v>
+        <v>768453</v>
       </c>
       <c r="R93" t="n">
-        <v>7085143</v>
+        <v>7085131</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11224,6 +11228,11 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11240,10 +11249,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622735</v>
+        <v>123622717</v>
       </c>
       <c r="B94" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11256,34 +11265,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768515</v>
+        <v>768463</v>
       </c>
       <c r="R94" t="n">
-        <v>7085140</v>
+        <v>7085126</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11336,6 +11345,11 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11352,10 +11366,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622731</v>
+        <v>123622735</v>
       </c>
       <c r="B95" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11392,10 +11406,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768463</v>
+        <v>768515</v>
       </c>
       <c r="R95" t="n">
-        <v>7085154</v>
+        <v>7085140</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11464,10 +11478,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622733</v>
+        <v>123622701</v>
       </c>
       <c r="B96" t="n">
-        <v>78805</v>
+        <v>78786</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11476,38 +11490,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768511</v>
+        <v>768642</v>
       </c>
       <c r="R96" t="n">
-        <v>7085142</v>
+        <v>7084688</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11576,10 +11590,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622725</v>
+        <v>123622718</v>
       </c>
       <c r="B97" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11612,14 +11626,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768375</v>
+        <v>768450</v>
       </c>
       <c r="R97" t="n">
-        <v>7085205</v>
+        <v>7085128</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11688,10 +11702,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622702</v>
+        <v>123622733</v>
       </c>
       <c r="B98" t="n">
-        <v>78781</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11700,38 +11714,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768615</v>
+        <v>768511</v>
       </c>
       <c r="R98" t="n">
-        <v>7084711</v>
+        <v>7085142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11800,10 +11814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622737</v>
+        <v>123622729</v>
       </c>
       <c r="B99" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11816,34 +11830,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768519</v>
+        <v>768416</v>
       </c>
       <c r="R99" t="n">
-        <v>7085133</v>
+        <v>7085204</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11888,6 +11907,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11899,7 +11923,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>döda granar</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11917,10 +11941,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622709</v>
+        <v>123622667</v>
       </c>
       <c r="B100" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11953,14 +11977,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768616</v>
+        <v>768557</v>
       </c>
       <c r="R100" t="n">
-        <v>7084853</v>
+        <v>7085109</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12029,10 +12053,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622670</v>
+        <v>123622703</v>
       </c>
       <c r="B101" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12069,10 +12093,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768634</v>
+        <v>768619</v>
       </c>
       <c r="R101" t="n">
-        <v>7084898</v>
+        <v>7084757</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12141,10 +12165,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622717</v>
+        <v>123622714</v>
       </c>
       <c r="B102" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12157,21 +12181,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12181,10 +12205,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768463</v>
+        <v>768493</v>
       </c>
       <c r="R102" t="n">
-        <v>7085126</v>
+        <v>7085068</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12237,11 +12261,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12258,10 +12277,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622706</v>
+        <v>123622713</v>
       </c>
       <c r="B103" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12294,14 +12313,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768635</v>
+        <v>768497</v>
       </c>
       <c r="R103" t="n">
-        <v>7084793</v>
+        <v>7085012</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12370,10 +12389,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622719</v>
+        <v>123622723</v>
       </c>
       <c r="B104" t="n">
-        <v>79317</v>
+        <v>78786</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12386,21 +12405,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12410,10 +12429,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768453</v>
+        <v>768385</v>
       </c>
       <c r="R104" t="n">
-        <v>7085131</v>
+        <v>7085111</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12466,11 +12485,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12487,10 +12501,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622716</v>
+        <v>123622670</v>
       </c>
       <c r="B105" t="n">
-        <v>79317</v>
+        <v>78786</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12503,34 +12517,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768463</v>
+        <v>768634</v>
       </c>
       <c r="R105" t="n">
-        <v>7085126</v>
+        <v>7084898</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12583,11 +12597,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12604,10 +12613,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622701</v>
+        <v>123622665</v>
       </c>
       <c r="B106" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12640,14 +12649,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768642</v>
+        <v>768559</v>
       </c>
       <c r="R106" t="n">
-        <v>7084688</v>
+        <v>7085175</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12716,10 +12725,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622711</v>
+        <v>123622710</v>
       </c>
       <c r="B107" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12732,34 +12741,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768579</v>
+        <v>768591</v>
       </c>
       <c r="R107" t="n">
-        <v>7084911</v>
+        <v>7084882</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12804,6 +12818,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12812,6 +12831,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12828,10 +12852,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622720</v>
+        <v>123622727</v>
       </c>
       <c r="B108" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12864,14 +12888,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768441</v>
+        <v>768402</v>
       </c>
       <c r="R108" t="n">
-        <v>7085131</v>
+        <v>7085218</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12940,10 +12964,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622704</v>
+        <v>123622737</v>
       </c>
       <c r="B109" t="n">
-        <v>56689</v>
+        <v>79867</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12956,51 +12980,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768617</v>
+        <v>768519</v>
       </c>
       <c r="R109" t="n">
-        <v>7084779</v>
+        <v>7085133</v>
       </c>
       <c r="S109" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13050,6 +13060,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13066,10 +13081,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622703</v>
+        <v>123622716</v>
       </c>
       <c r="B110" t="n">
-        <v>78781</v>
+        <v>79322</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13082,34 +13097,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768619</v>
+        <v>768463</v>
       </c>
       <c r="R110" t="n">
-        <v>7084757</v>
+        <v>7085126</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13162,6 +13177,11 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13178,10 +13198,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622712</v>
+        <v>123622726</v>
       </c>
       <c r="B111" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13214,14 +13234,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768522</v>
+        <v>768378</v>
       </c>
       <c r="R111" t="n">
-        <v>7084946</v>
+        <v>7085228</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13290,10 +13310,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622715</v>
+        <v>123622712</v>
       </c>
       <c r="B112" t="n">
-        <v>78813</v>
+        <v>78786</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13306,21 +13326,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13330,10 +13350,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768491</v>
+        <v>768522</v>
       </c>
       <c r="R112" t="n">
-        <v>7085072</v>
+        <v>7084946</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13402,10 +13422,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622705</v>
+        <v>123622732</v>
       </c>
       <c r="B113" t="n">
-        <v>90948</v>
+        <v>78786</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13414,38 +13434,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768635</v>
+        <v>768481</v>
       </c>
       <c r="R113" t="n">
-        <v>7084792</v>
+        <v>7085143</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13498,11 +13518,6 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13519,10 +13534,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622729</v>
+        <v>123622731</v>
       </c>
       <c r="B114" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13535,39 +13550,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768416</v>
+        <v>768463</v>
       </c>
       <c r="R114" t="n">
-        <v>7085204</v>
+        <v>7085154</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13612,11 +13622,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13625,11 +13630,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13646,10 +13646,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622730</v>
+        <v>123622725</v>
       </c>
       <c r="B115" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13686,10 +13686,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768457</v>
+        <v>768375</v>
       </c>
       <c r="R115" t="n">
-        <v>7085185</v>
+        <v>7085205</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13758,10 +13758,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123622714</v>
+        <v>123622666</v>
       </c>
       <c r="B116" t="n">
-        <v>78781</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13770,38 +13770,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>768493</v>
+        <v>768567</v>
       </c>
       <c r="R116" t="n">
-        <v>7085068</v>
+        <v>7085161</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119719108</v>
+        <v>119719079</v>
       </c>
       <c r="B46" t="n">
-        <v>74593</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5873,25 +5873,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>768434</v>
+        <v>768430</v>
       </c>
       <c r="R46" t="n">
-        <v>7085126</v>
+        <v>7085132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119719079</v>
+        <v>119719117</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>768430</v>
+        <v>768475</v>
       </c>
       <c r="R47" t="n">
-        <v>7085132</v>
+        <v>7084691</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119719117</v>
+        <v>119719118</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>768475</v>
+        <v>768519</v>
       </c>
       <c r="R48" t="n">
-        <v>7084691</v>
+        <v>7084683</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119719118</v>
+        <v>119719116</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768519</v>
+        <v>768521</v>
       </c>
       <c r="R49" t="n">
-        <v>7084683</v>
+        <v>7085096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119719116</v>
+        <v>119719069</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768521</v>
+        <v>768550</v>
       </c>
       <c r="R50" t="n">
-        <v>7085096</v>
+        <v>7084957</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119719069</v>
+        <v>119719070</v>
       </c>
       <c r="B51" t="n">
         <v>90545</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>768550</v>
+        <v>768558</v>
       </c>
       <c r="R51" t="n">
-        <v>7084957</v>
+        <v>7084827</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119719070</v>
+        <v>119719067</v>
       </c>
       <c r="B52" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6485,25 +6485,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>768558</v>
+        <v>768524</v>
       </c>
       <c r="R52" t="n">
-        <v>7084827</v>
+        <v>7085020</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119719067</v>
+        <v>120285903</v>
       </c>
       <c r="B53" t="n">
-        <v>78576</v>
+        <v>90597</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6587,25 +6587,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>768524</v>
+        <v>768552</v>
       </c>
       <c r="R53" t="n">
-        <v>7085020</v>
+        <v>7084960</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6670,17 +6670,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Emil Larsson, Julia Pettersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120285903</v>
+        <v>120285904</v>
       </c>
       <c r="B54" t="n">
-        <v>90597</v>
+        <v>90632</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6689,25 +6689,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>768552</v>
+        <v>768612</v>
       </c>
       <c r="R54" t="n">
-        <v>7084960</v>
+        <v>7084906</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120285904</v>
+        <v>120285901</v>
       </c>
       <c r="B55" t="n">
-        <v>90632</v>
+        <v>79642</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768612</v>
+        <v>768524</v>
       </c>
       <c r="R55" t="n">
-        <v>7084906</v>
+        <v>7085136</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120285901</v>
+        <v>120285905</v>
       </c>
       <c r="B56" t="n">
-        <v>79642</v>
+        <v>90597</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768524</v>
+        <v>768617</v>
       </c>
       <c r="R56" t="n">
-        <v>7085136</v>
+        <v>7084860</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120285905</v>
+        <v>120285906</v>
       </c>
       <c r="B57" t="n">
-        <v>90597</v>
+        <v>90579</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6995,25 +6995,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120285906</v>
+        <v>120469523</v>
       </c>
       <c r="B58" t="n">
-        <v>90579</v>
+        <v>57500</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,37 +7101,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Degersjön S, Vb</t>
+          <t>degersjön, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768617</v>
+        <v>768415</v>
       </c>
       <c r="R58" t="n">
-        <v>7084860</v>
+        <v>7085120</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7155,12 +7163,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7175,22 +7183,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil Larsson, Julia Pettersson</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120469523</v>
+        <v>120469533</v>
       </c>
       <c r="B59" t="n">
-        <v>57500</v>
+        <v>94448</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7199,35 +7207,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7235,10 +7239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>768415</v>
+        <v>768525</v>
       </c>
       <c r="R59" t="n">
-        <v>7085120</v>
+        <v>7085190</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7279,6 +7283,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7297,10 +7302,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120469533</v>
+        <v>120469518</v>
       </c>
       <c r="B60" t="n">
-        <v>94448</v>
+        <v>79674</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7309,31 +7314,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7344,7 +7348,7 @@
         <v>768525</v>
       </c>
       <c r="R60" t="n">
-        <v>7085190</v>
+        <v>7085170</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7404,10 +7408,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120469518</v>
+        <v>120792882</v>
       </c>
       <c r="B61" t="n">
-        <v>79674</v>
+        <v>90662</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7416,44 +7420,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>degersjön, Vb</t>
+          <t>Skogen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>768525</v>
+        <v>768429</v>
       </c>
       <c r="R61" t="n">
-        <v>7085170</v>
+        <v>7085236</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7491,29 +7492,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Olov Tranberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120792882</v>
+        <v>120792881</v>
       </c>
       <c r="B62" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7522,25 +7522,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120792881</v>
+        <v>120813701</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7628,37 +7628,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skogen, Vb</t>
+          <t>Degersjön Södra, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>768429</v>
+        <v>768518</v>
       </c>
       <c r="R63" t="n">
-        <v>7085236</v>
+        <v>7084868</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7682,12 +7690,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Hackspår på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7702,22 +7715,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Olov Tranberg</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120813701</v>
+        <v>121169083</v>
       </c>
       <c r="B64" t="n">
-        <v>57367</v>
+        <v>90666</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7730,45 +7743,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Degersjön Södra, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>768518</v>
+        <v>768563</v>
       </c>
       <c r="R64" t="n">
-        <v>7084868</v>
+        <v>7084836</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7792,17 +7797,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Hackspår på gran</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7813,26 +7813,46 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Granlåga, mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, mossbevuxen</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121169083</v>
+        <v>121169094</v>
       </c>
       <c r="B65" t="n">
-        <v>90666</v>
+        <v>57371</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,34 +7865,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>768563</v>
+        <v>768518</v>
       </c>
       <c r="R65" t="n">
-        <v>7084836</v>
+        <v>7085159</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7907,6 +7935,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7918,22 +7951,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Granlåga, mossbevuxen</t>
+          <t>Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, mossbevuxen</t>
+          <t>Populus tremula # Med lunglav och bohål</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7951,10 +7984,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121169094</v>
+        <v>121169095</v>
       </c>
       <c r="B66" t="n">
-        <v>57371</v>
+        <v>79689</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7967,31 +8000,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8039,7 +8067,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8048,6 +8076,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8061,14 +8090,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Med lunglav och bohål</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Populus tremula # Med lunglav och bohål</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8086,10 +8110,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121169095</v>
+        <v>121169087</v>
       </c>
       <c r="B67" t="n">
-        <v>79689</v>
+        <v>57371</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8102,37 +8126,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>768518</v>
+        <v>768530</v>
       </c>
       <c r="R67" t="n">
-        <v>7085159</v>
+        <v>7084802</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8169,7 +8195,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav, bohål större, troligen spillkråka</t>
+          <t>Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8178,23 +8204,27 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8212,10 +8242,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121169087</v>
+        <v>121169107</v>
       </c>
       <c r="B68" t="n">
-        <v>57371</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8228,39 +8258,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>768530</v>
+        <v>768518</v>
       </c>
       <c r="R68" t="n">
-        <v>7084802</v>
+        <v>7085102</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8295,11 +8320,6 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8311,22 +8331,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Stående levande</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Pinus sylvestris # Stående levande</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8344,7 +8364,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121169107</v>
+        <v>121169108</v>
       </c>
       <c r="B69" t="n">
         <v>78608</v>
@@ -8384,10 +8404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>768518</v>
+        <v>768544</v>
       </c>
       <c r="R69" t="n">
-        <v>7085102</v>
+        <v>7085156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8433,12 +8453,12 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
@@ -8448,7 +8468,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Stående levande</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8466,10 +8486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121169108</v>
+        <v>121169084</v>
       </c>
       <c r="B70" t="n">
-        <v>78608</v>
+        <v>57371</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8482,34 +8502,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>768544</v>
+        <v>768481</v>
       </c>
       <c r="R70" t="n">
-        <v>7085156</v>
+        <v>7085107</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8544,6 +8569,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8555,22 +8585,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Stående levande</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8588,10 +8618,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121169084</v>
+        <v>121169097</v>
       </c>
       <c r="B71" t="n">
-        <v>57371</v>
+        <v>57724</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8600,20 +8630,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8622,21 +8652,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>768481</v>
+        <v>768571</v>
       </c>
       <c r="R71" t="n">
-        <v>7085107</v>
+        <v>7084796</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8666,14 +8699,19 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8684,26 +8722,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Silverfura</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Silverfura</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8720,10 +8738,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121169097</v>
+        <v>121169106</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>78608</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8732,46 +8750,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>768571</v>
+        <v>768519</v>
       </c>
       <c r="R72" t="n">
-        <v>7084796</v>
+        <v>7085101</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8801,21 +8811,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-10</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8824,6 +8824,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Stående levande</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Stående levande</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8840,10 +8860,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121169106</v>
+        <v>121169078</v>
       </c>
       <c r="B73" t="n">
-        <v>78608</v>
+        <v>90684</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8852,25 +8872,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8880,10 +8900,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>768519</v>
+        <v>768549</v>
       </c>
       <c r="R73" t="n">
-        <v>7085101</v>
+        <v>7084957</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8929,22 +8949,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Stående levande</t>
+          <t>Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Stående levande</t>
+          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8962,10 +8982,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121169078</v>
+        <v>121169103</v>
       </c>
       <c r="B74" t="n">
-        <v>90684</v>
+        <v>90737</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8974,25 +8994,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9002,10 +9022,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>768549</v>
+        <v>768584</v>
       </c>
       <c r="R74" t="n">
-        <v>7084957</v>
+        <v>7084948</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9040,6 +9060,11 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9061,12 +9086,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Granlågor, 2 lågor bredvid varandra</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies # Granlågor, 2 lågor bredvid varandra</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9084,10 +9109,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121169103</v>
+        <v>121169093</v>
       </c>
       <c r="B75" t="n">
-        <v>90737</v>
+        <v>79689</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9100,34 +9125,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>768584</v>
+        <v>768523</v>
       </c>
       <c r="R75" t="n">
-        <v>7084948</v>
+        <v>7085140</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9164,7 +9192,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9173,27 +9201,23 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Stående död</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9211,10 +9235,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121169093</v>
+        <v>121169085</v>
       </c>
       <c r="B76" t="n">
-        <v>79689</v>
+        <v>57371</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9227,37 +9251,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>768523</v>
+        <v>768500</v>
       </c>
       <c r="R76" t="n">
-        <v>7085140</v>
+        <v>7085111</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9294,7 +9320,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav högt upp, även 2 bohål. Lunglav på asp i närheten. Ingen hänsynssnitsel</t>
+          <t>Äldre spår vid basen</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9303,23 +9329,27 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Basen av silverfuran</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris # Basen av silverfuran</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9337,10 +9367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121169085</v>
+        <v>121595937</v>
       </c>
       <c r="B77" t="n">
-        <v>57371</v>
+        <v>57518</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9353,42 +9383,49 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>768500</v>
+        <v>768640</v>
       </c>
       <c r="R77" t="n">
-        <v>7085111</v>
+        <v>7085029</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9412,17 +9449,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre spår vid basen</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9433,46 +9465,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Basen av silverfuran</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Basen av silverfuran</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring, Carl Jansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121595937</v>
+        <v>122951644</v>
       </c>
       <c r="B78" t="n">
-        <v>57518</v>
+        <v>78813</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9485,49 +9497,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>768640</v>
+        <v>768631</v>
       </c>
       <c r="R78" t="n">
-        <v>7085029</v>
+        <v>7084761</v>
       </c>
       <c r="S78" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9551,12 +9551,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9576,17 +9576,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Carl Jansson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122951644</v>
+        <v>122951641</v>
       </c>
       <c r="B79" t="n">
-        <v>78813</v>
+        <v>78805</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9595,38 +9595,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>768631</v>
+        <v>768458</v>
       </c>
       <c r="R79" t="n">
-        <v>7084761</v>
+        <v>7084852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9685,10 +9685,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122951641</v>
+        <v>122951645</v>
       </c>
       <c r="B80" t="n">
-        <v>78805</v>
+        <v>78781</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9697,38 +9697,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stubbmyran, Ultervik, Vb</t>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>768458</v>
+        <v>768634</v>
       </c>
       <c r="R80" t="n">
-        <v>7084852</v>
+        <v>7084758</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9787,7 +9787,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122951645</v>
+        <v>122951643</v>
       </c>
       <c r="B81" t="n">
         <v>78781</v>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>768634</v>
+        <v>768541</v>
       </c>
       <c r="R81" t="n">
-        <v>7084758</v>
+        <v>7084820</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9889,10 +9889,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122951643</v>
+        <v>122951724</v>
       </c>
       <c r="B82" t="n">
-        <v>78781</v>
+        <v>57857</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9901,41 +9901,53 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>768541</v>
+        <v>768640</v>
       </c>
       <c r="R82" t="n">
-        <v>7084820</v>
+        <v>7085029</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9991,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122951724</v>
+        <v>123622727</v>
       </c>
       <c r="B83" t="n">
-        <v>57857</v>
+        <v>78788</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10003,53 +10015,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>vid Spångmyran, Ulterviksvägen, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768640</v>
+        <v>768402</v>
       </c>
       <c r="R83" t="n">
-        <v>7085029</v>
+        <v>7085218</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10073,12 +10073,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10105,10 +10115,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622709</v>
+        <v>123622731</v>
       </c>
       <c r="B84" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10141,14 +10151,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768616</v>
+        <v>768463</v>
       </c>
       <c r="R84" t="n">
-        <v>7084853</v>
+        <v>7085154</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10217,10 +10227,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622706</v>
+        <v>123622714</v>
       </c>
       <c r="B85" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10253,14 +10263,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768635</v>
+        <v>768493</v>
       </c>
       <c r="R85" t="n">
-        <v>7084793</v>
+        <v>7085068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10329,10 +10339,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622702</v>
+        <v>123622732</v>
       </c>
       <c r="B86" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10365,14 +10375,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768615</v>
+        <v>768481</v>
       </c>
       <c r="R86" t="n">
-        <v>7084711</v>
+        <v>7085143</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10441,10 +10451,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622711</v>
+        <v>123622730</v>
       </c>
       <c r="B87" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10477,14 +10487,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768579</v>
+        <v>768457</v>
       </c>
       <c r="R87" t="n">
-        <v>7084911</v>
+        <v>7085185</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10553,10 +10563,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622705</v>
+        <v>123622704</v>
       </c>
       <c r="B88" t="n">
-        <v>90953</v>
+        <v>56692</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10565,41 +10575,55 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768635</v>
+        <v>768617</v>
       </c>
       <c r="R88" t="n">
-        <v>7084792</v>
+        <v>7084779</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10649,11 +10673,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10670,10 +10689,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622730</v>
+        <v>123622703</v>
       </c>
       <c r="B89" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10706,14 +10725,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768457</v>
+        <v>768619</v>
       </c>
       <c r="R89" t="n">
-        <v>7085185</v>
+        <v>7084757</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10782,10 +10801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622704</v>
+        <v>123622706</v>
       </c>
       <c r="B90" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10798,51 +10817,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768617</v>
+        <v>768635</v>
       </c>
       <c r="R90" t="n">
-        <v>7084779</v>
+        <v>7084793</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10908,10 +10913,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622720</v>
+        <v>123622670</v>
       </c>
       <c r="B91" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10944,14 +10949,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768441</v>
+        <v>768634</v>
       </c>
       <c r="R91" t="n">
-        <v>7085131</v>
+        <v>7084898</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11020,10 +11025,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622715</v>
+        <v>123622725</v>
       </c>
       <c r="B92" t="n">
-        <v>78818</v>
+        <v>78788</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11036,34 +11041,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768491</v>
+        <v>768375</v>
       </c>
       <c r="R92" t="n">
-        <v>7085072</v>
+        <v>7085205</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11132,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622719</v>
+        <v>123622665</v>
       </c>
       <c r="B93" t="n">
-        <v>79322</v>
+        <v>78788</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11148,34 +11153,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768453</v>
+        <v>768559</v>
       </c>
       <c r="R93" t="n">
-        <v>7085131</v>
+        <v>7085175</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11228,11 +11233,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11249,10 +11249,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622717</v>
+        <v>123622702</v>
       </c>
       <c r="B94" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11265,34 +11265,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768463</v>
+        <v>768615</v>
       </c>
       <c r="R94" t="n">
-        <v>7085126</v>
+        <v>7084711</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11345,11 +11345,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11366,10 +11361,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622735</v>
+        <v>123622733</v>
       </c>
       <c r="B95" t="n">
-        <v>78786</v>
+        <v>78812</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11378,25 +11373,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11406,10 +11401,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768515</v>
+        <v>768511</v>
       </c>
       <c r="R95" t="n">
-        <v>7085140</v>
+        <v>7085142</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11478,10 +11473,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622701</v>
+        <v>123622723</v>
       </c>
       <c r="B96" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11514,14 +11509,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768642</v>
+        <v>768385</v>
       </c>
       <c r="R96" t="n">
-        <v>7084688</v>
+        <v>7085111</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11590,10 +11585,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622718</v>
+        <v>123622715</v>
       </c>
       <c r="B97" t="n">
-        <v>78786</v>
+        <v>78820</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11606,21 +11601,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11630,10 +11625,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768450</v>
+        <v>768491</v>
       </c>
       <c r="R97" t="n">
-        <v>7085128</v>
+        <v>7085072</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11702,10 +11697,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622733</v>
+        <v>123622719</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>79324</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11714,38 +11709,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6434</v>
+        <v>1352</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768511</v>
+        <v>768453</v>
       </c>
       <c r="R98" t="n">
-        <v>7085142</v>
+        <v>7085131</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11798,6 +11793,11 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11814,10 +11814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622729</v>
+        <v>123622701</v>
       </c>
       <c r="B99" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11830,39 +11830,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768416</v>
+        <v>768642</v>
       </c>
       <c r="R99" t="n">
-        <v>7085204</v>
+        <v>7084688</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11907,11 +11902,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11920,11 +11910,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11941,10 +11926,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622667</v>
+        <v>123622712</v>
       </c>
       <c r="B100" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11977,14 +11962,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768557</v>
+        <v>768522</v>
       </c>
       <c r="R100" t="n">
-        <v>7085109</v>
+        <v>7084946</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12053,10 +12038,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622703</v>
+        <v>123622729</v>
       </c>
       <c r="B101" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12069,34 +12054,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768619</v>
+        <v>768416</v>
       </c>
       <c r="R101" t="n">
-        <v>7084757</v>
+        <v>7085204</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12141,6 +12131,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12149,6 +12144,11 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12165,10 +12165,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622714</v>
+        <v>123622710</v>
       </c>
       <c r="B102" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12181,34 +12181,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768493</v>
+        <v>768591</v>
       </c>
       <c r="R102" t="n">
-        <v>7085068</v>
+        <v>7084882</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12253,6 +12258,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12261,6 +12271,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12277,10 +12292,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622713</v>
+        <v>123622726</v>
       </c>
       <c r="B103" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12313,14 +12328,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768497</v>
+        <v>768378</v>
       </c>
       <c r="R103" t="n">
-        <v>7085012</v>
+        <v>7085228</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12389,10 +12404,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622723</v>
+        <v>123622735</v>
       </c>
       <c r="B104" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12425,14 +12440,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768385</v>
+        <v>768515</v>
       </c>
       <c r="R104" t="n">
-        <v>7085111</v>
+        <v>7085140</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12501,10 +12516,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622670</v>
+        <v>123622666</v>
       </c>
       <c r="B105" t="n">
-        <v>78786</v>
+        <v>78812</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12513,38 +12528,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768634</v>
+        <v>768567</v>
       </c>
       <c r="R105" t="n">
-        <v>7084898</v>
+        <v>7085161</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12613,10 +12628,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622665</v>
+        <v>123622705</v>
       </c>
       <c r="B106" t="n">
-        <v>78786</v>
+        <v>90955</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12625,38 +12640,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768559</v>
+        <v>768635</v>
       </c>
       <c r="R106" t="n">
-        <v>7085175</v>
+        <v>7084792</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12709,6 +12724,11 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12725,10 +12745,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622710</v>
+        <v>123622720</v>
       </c>
       <c r="B107" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12741,39 +12761,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768591</v>
+        <v>768441</v>
       </c>
       <c r="R107" t="n">
-        <v>7084882</v>
+        <v>7085131</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12818,11 +12833,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12831,11 +12841,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12852,10 +12857,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622727</v>
+        <v>123622709</v>
       </c>
       <c r="B108" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12888,14 +12893,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768402</v>
+        <v>768616</v>
       </c>
       <c r="R108" t="n">
-        <v>7085218</v>
+        <v>7084853</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12967,7 +12972,7 @@
         <v>123622737</v>
       </c>
       <c r="B109" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13081,10 +13086,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622716</v>
+        <v>123622717</v>
       </c>
       <c r="B110" t="n">
-        <v>79322</v>
+        <v>79869</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13097,21 +13102,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1352</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13198,10 +13203,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622726</v>
+        <v>123622713</v>
       </c>
       <c r="B111" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13234,14 +13239,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768378</v>
+        <v>768497</v>
       </c>
       <c r="R111" t="n">
-        <v>7085228</v>
+        <v>7085012</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13310,10 +13315,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622712</v>
+        <v>123622667</v>
       </c>
       <c r="B112" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13346,14 +13351,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768522</v>
+        <v>768557</v>
       </c>
       <c r="R112" t="n">
-        <v>7084946</v>
+        <v>7085109</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13422,10 +13427,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622732</v>
+        <v>123622718</v>
       </c>
       <c r="B113" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13458,14 +13463,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768481</v>
+        <v>768450</v>
       </c>
       <c r="R113" t="n">
-        <v>7085143</v>
+        <v>7085128</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13534,10 +13539,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622731</v>
+        <v>123622716</v>
       </c>
       <c r="B114" t="n">
-        <v>78786</v>
+        <v>79324</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13550,34 +13555,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
         <v>768463</v>
       </c>
       <c r="R114" t="n">
-        <v>7085154</v>
+        <v>7085126</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13630,6 +13635,11 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13646,10 +13656,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622725</v>
+        <v>123622711</v>
       </c>
       <c r="B115" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13682,14 +13692,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768375</v>
+        <v>768579</v>
       </c>
       <c r="R115" t="n">
-        <v>7085205</v>
+        <v>7084911</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13755,118 +13765,6 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>123622666</v>
-      </c>
-      <c r="B116" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>6434</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Nästlav</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Bryoria furcellata</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
-        </is>
-      </c>
-      <c r="Q116" t="n">
-        <v>768567</v>
-      </c>
-      <c r="R116" t="n">
-        <v>7085161</v>
-      </c>
-      <c r="S116" t="n">
-        <v>10</v>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AD116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT116" t="inlineStr"/>
-      <c r="AW116" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123622727</v>
+        <v>123622719</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10019,34 +10019,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768402</v>
+        <v>768453</v>
       </c>
       <c r="R83" t="n">
-        <v>7085218</v>
+        <v>7085131</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10099,6 +10099,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10115,10 +10120,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622731</v>
+        <v>123622666</v>
       </c>
       <c r="B84" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10127,25 +10132,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10155,10 +10160,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768463</v>
+        <v>768567</v>
       </c>
       <c r="R84" t="n">
-        <v>7085154</v>
+        <v>7085161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10227,7 +10232,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622714</v>
+        <v>123622702</v>
       </c>
       <c r="B85" t="n">
         <v>78788</v>
@@ -10263,14 +10268,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768493</v>
+        <v>768615</v>
       </c>
       <c r="R85" t="n">
-        <v>7085068</v>
+        <v>7084711</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10339,7 +10344,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622732</v>
+        <v>123622735</v>
       </c>
       <c r="B86" t="n">
         <v>78788</v>
@@ -10379,10 +10384,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768481</v>
+        <v>768515</v>
       </c>
       <c r="R86" t="n">
-        <v>7085143</v>
+        <v>7085140</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10451,7 +10456,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622730</v>
+        <v>123622731</v>
       </c>
       <c r="B87" t="n">
         <v>78788</v>
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768457</v>
+        <v>768463</v>
       </c>
       <c r="R87" t="n">
-        <v>7085185</v>
+        <v>7085154</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10563,10 +10568,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622704</v>
+        <v>123622732</v>
       </c>
       <c r="B88" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10579,51 +10584,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768617</v>
+        <v>768481</v>
       </c>
       <c r="R88" t="n">
-        <v>7084779</v>
+        <v>7085143</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10689,7 +10680,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622703</v>
+        <v>123622701</v>
       </c>
       <c r="B89" t="n">
         <v>78788</v>
@@ -10729,10 +10720,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768619</v>
+        <v>768642</v>
       </c>
       <c r="R89" t="n">
-        <v>7084757</v>
+        <v>7084688</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10801,7 +10792,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622706</v>
+        <v>123622670</v>
       </c>
       <c r="B90" t="n">
         <v>78788</v>
@@ -10841,10 +10832,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768635</v>
+        <v>768634</v>
       </c>
       <c r="R90" t="n">
-        <v>7084793</v>
+        <v>7084898</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10913,7 +10904,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622670</v>
+        <v>123622667</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -10949,14 +10940,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768634</v>
+        <v>768557</v>
       </c>
       <c r="R91" t="n">
-        <v>7084898</v>
+        <v>7085109</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11025,7 +11016,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622725</v>
+        <v>123622712</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -11061,14 +11052,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768375</v>
+        <v>768522</v>
       </c>
       <c r="R92" t="n">
-        <v>7085205</v>
+        <v>7084946</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11137,7 +11128,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622665</v>
+        <v>123622711</v>
       </c>
       <c r="B93" t="n">
         <v>78788</v>
@@ -11173,14 +11164,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768559</v>
+        <v>768579</v>
       </c>
       <c r="R93" t="n">
-        <v>7085175</v>
+        <v>7084911</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11249,7 +11240,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622702</v>
+        <v>123622725</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11285,14 +11276,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768615</v>
+        <v>768375</v>
       </c>
       <c r="R94" t="n">
-        <v>7084711</v>
+        <v>7085205</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11361,10 +11352,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622733</v>
+        <v>123622737</v>
       </c>
       <c r="B95" t="n">
-        <v>78812</v>
+        <v>79869</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11373,25 +11364,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11401,10 +11392,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768511</v>
+        <v>768519</v>
       </c>
       <c r="R95" t="n">
-        <v>7085142</v>
+        <v>7085133</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11457,6 +11448,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11473,7 +11469,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622723</v>
+        <v>123622714</v>
       </c>
       <c r="B96" t="n">
         <v>78788</v>
@@ -11513,10 +11509,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768385</v>
+        <v>768493</v>
       </c>
       <c r="R96" t="n">
-        <v>7085111</v>
+        <v>7085068</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11585,10 +11581,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622715</v>
+        <v>123622716</v>
       </c>
       <c r="B97" t="n">
-        <v>78820</v>
+        <v>79324</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11601,21 +11597,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>1352</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11625,10 +11621,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768491</v>
+        <v>768463</v>
       </c>
       <c r="R97" t="n">
-        <v>7085072</v>
+        <v>7085126</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11681,6 +11677,11 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11697,10 +11698,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622719</v>
+        <v>123622665</v>
       </c>
       <c r="B98" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11713,34 +11714,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768453</v>
+        <v>768559</v>
       </c>
       <c r="R98" t="n">
-        <v>7085131</v>
+        <v>7085175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11793,11 +11794,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11814,7 +11810,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622701</v>
+        <v>123622706</v>
       </c>
       <c r="B99" t="n">
         <v>78788</v>
@@ -11854,10 +11850,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768642</v>
+        <v>768635</v>
       </c>
       <c r="R99" t="n">
-        <v>7084688</v>
+        <v>7084793</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11926,7 +11922,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622712</v>
+        <v>123622720</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -11966,10 +11962,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768522</v>
+        <v>768441</v>
       </c>
       <c r="R100" t="n">
-        <v>7084946</v>
+        <v>7085131</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12038,10 +12034,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622729</v>
+        <v>123622705</v>
       </c>
       <c r="B101" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12050,43 +12046,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768416</v>
+        <v>768635</v>
       </c>
       <c r="R101" t="n">
-        <v>7085204</v>
+        <v>7084792</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12131,11 +12122,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12147,7 +12133,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>döda granar</t>
+          <t>grangrenar död gran</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -12165,10 +12151,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622710</v>
+        <v>123622730</v>
       </c>
       <c r="B102" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12181,39 +12167,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768591</v>
+        <v>768457</v>
       </c>
       <c r="R102" t="n">
-        <v>7084882</v>
+        <v>7085185</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12258,11 +12239,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12271,11 +12247,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12292,10 +12263,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622726</v>
+        <v>123622704</v>
       </c>
       <c r="B103" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12308,37 +12279,51 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768378</v>
+        <v>768617</v>
       </c>
       <c r="R103" t="n">
-        <v>7085228</v>
+        <v>7084779</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12404,10 +12389,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622735</v>
+        <v>123622729</v>
       </c>
       <c r="B104" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12420,34 +12405,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768515</v>
+        <v>768416</v>
       </c>
       <c r="R104" t="n">
-        <v>7085140</v>
+        <v>7085204</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12492,6 +12482,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12500,6 +12495,11 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12516,7 +12516,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622666</v>
+        <v>123622733</v>
       </c>
       <c r="B105" t="n">
         <v>78812</v>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768567</v>
+        <v>768511</v>
       </c>
       <c r="R105" t="n">
-        <v>7085161</v>
+        <v>7085142</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12628,10 +12628,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622705</v>
+        <v>123622713</v>
       </c>
       <c r="B106" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12640,38 +12640,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768635</v>
+        <v>768497</v>
       </c>
       <c r="R106" t="n">
-        <v>7084792</v>
+        <v>7085012</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12724,11 +12724,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12745,10 +12740,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622720</v>
+        <v>123622717</v>
       </c>
       <c r="B107" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12761,21 +12756,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12785,10 +12780,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768441</v>
+        <v>768463</v>
       </c>
       <c r="R107" t="n">
-        <v>7085131</v>
+        <v>7085126</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12841,6 +12836,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12857,7 +12857,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622709</v>
+        <v>123622723</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -12893,14 +12893,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768616</v>
+        <v>768385</v>
       </c>
       <c r="R108" t="n">
-        <v>7084853</v>
+        <v>7085111</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12969,10 +12969,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622737</v>
+        <v>123622703</v>
       </c>
       <c r="B109" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12985,34 +12985,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768519</v>
+        <v>768619</v>
       </c>
       <c r="R109" t="n">
-        <v>7085133</v>
+        <v>7084757</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13065,11 +13065,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13086,10 +13081,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622717</v>
+        <v>123622726</v>
       </c>
       <c r="B110" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13102,34 +13097,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768463</v>
+        <v>768378</v>
       </c>
       <c r="R110" t="n">
-        <v>7085126</v>
+        <v>7085228</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13182,11 +13177,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13203,7 +13193,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622713</v>
+        <v>123622709</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -13239,14 +13229,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768497</v>
+        <v>768616</v>
       </c>
       <c r="R111" t="n">
-        <v>7085012</v>
+        <v>7084853</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13315,7 +13305,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622667</v>
+        <v>123622718</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -13351,14 +13341,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768557</v>
+        <v>768450</v>
       </c>
       <c r="R112" t="n">
-        <v>7085109</v>
+        <v>7085128</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13427,10 +13417,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622718</v>
+        <v>123622710</v>
       </c>
       <c r="B113" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13443,34 +13433,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768450</v>
+        <v>768591</v>
       </c>
       <c r="R113" t="n">
-        <v>7085128</v>
+        <v>7084882</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13515,6 +13510,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13523,6 +13523,11 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13539,10 +13544,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622716</v>
+        <v>123622715</v>
       </c>
       <c r="B114" t="n">
-        <v>79324</v>
+        <v>78820</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13555,21 +13560,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1352</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13579,10 +13584,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768463</v>
+        <v>768491</v>
       </c>
       <c r="R114" t="n">
-        <v>7085126</v>
+        <v>7085072</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13635,11 +13640,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13656,7 +13656,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622711</v>
+        <v>123622727</v>
       </c>
       <c r="B115" t="n">
         <v>78788</v>
@@ -13692,14 +13692,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768579</v>
+        <v>768402</v>
       </c>
       <c r="R115" t="n">
-        <v>7084911</v>
+        <v>7085218</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -12389,10 +12389,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622729</v>
+        <v>123622733</v>
       </c>
       <c r="B104" t="n">
-        <v>57491</v>
+        <v>78812</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12401,43 +12401,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768416</v>
+        <v>768511</v>
       </c>
       <c r="R104" t="n">
-        <v>7085204</v>
+        <v>7085142</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12482,11 +12477,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12495,11 +12485,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12516,10 +12501,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622733</v>
+        <v>123622729</v>
       </c>
       <c r="B105" t="n">
-        <v>78812</v>
+        <v>57491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12528,38 +12513,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768511</v>
+        <v>768416</v>
       </c>
       <c r="R105" t="n">
-        <v>7085142</v>
+        <v>7085204</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12604,6 +12594,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12612,6 +12607,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123622719</v>
+        <v>123622727</v>
       </c>
       <c r="B83" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10019,34 +10019,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768453</v>
+        <v>768402</v>
       </c>
       <c r="R83" t="n">
-        <v>7085131</v>
+        <v>7085218</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10099,11 +10099,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10120,10 +10115,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622666</v>
+        <v>123622732</v>
       </c>
       <c r="B84" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10132,25 +10127,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10160,10 +10155,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768567</v>
+        <v>768481</v>
       </c>
       <c r="R84" t="n">
-        <v>7085161</v>
+        <v>7085143</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10232,10 +10227,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622702</v>
+        <v>123622719</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10248,34 +10243,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768615</v>
+        <v>768453</v>
       </c>
       <c r="R85" t="n">
-        <v>7084711</v>
+        <v>7085131</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10328,6 +10323,11 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10344,10 +10344,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622735</v>
+        <v>123622715</v>
       </c>
       <c r="B86" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10360,34 +10360,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768515</v>
+        <v>768491</v>
       </c>
       <c r="R86" t="n">
-        <v>7085140</v>
+        <v>7085072</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10456,7 +10456,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622731</v>
+        <v>123622706</v>
       </c>
       <c r="B87" t="n">
         <v>78788</v>
@@ -10492,14 +10492,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768463</v>
+        <v>768635</v>
       </c>
       <c r="R87" t="n">
-        <v>7085154</v>
+        <v>7084793</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622732</v>
+        <v>123622667</v>
       </c>
       <c r="B88" t="n">
         <v>78788</v>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768481</v>
+        <v>768557</v>
       </c>
       <c r="R88" t="n">
-        <v>7085143</v>
+        <v>7085109</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10680,7 +10680,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622701</v>
+        <v>123622714</v>
       </c>
       <c r="B89" t="n">
         <v>78788</v>
@@ -10716,14 +10716,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768642</v>
+        <v>768493</v>
       </c>
       <c r="R89" t="n">
-        <v>7084688</v>
+        <v>7085068</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10792,10 +10792,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622670</v>
+        <v>123622737</v>
       </c>
       <c r="B90" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10808,34 +10808,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768634</v>
+        <v>768519</v>
       </c>
       <c r="R90" t="n">
-        <v>7084898</v>
+        <v>7085133</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10888,6 +10888,11 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10904,7 +10909,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622667</v>
+        <v>123622723</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -10940,14 +10945,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768557</v>
+        <v>768385</v>
       </c>
       <c r="R91" t="n">
-        <v>7085109</v>
+        <v>7085111</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11016,7 +11021,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622712</v>
+        <v>123622725</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -11052,14 +11057,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768522</v>
+        <v>768375</v>
       </c>
       <c r="R92" t="n">
-        <v>7084946</v>
+        <v>7085205</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11128,7 +11133,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622711</v>
+        <v>123622718</v>
       </c>
       <c r="B93" t="n">
         <v>78788</v>
@@ -11164,14 +11169,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768579</v>
+        <v>768450</v>
       </c>
       <c r="R93" t="n">
-        <v>7084911</v>
+        <v>7085128</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11240,7 +11245,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622725</v>
+        <v>123622713</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11276,14 +11281,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768375</v>
+        <v>768497</v>
       </c>
       <c r="R94" t="n">
-        <v>7085205</v>
+        <v>7085012</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,10 +11357,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622737</v>
+        <v>123622710</v>
       </c>
       <c r="B95" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11368,34 +11373,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768519</v>
+        <v>768591</v>
       </c>
       <c r="R95" t="n">
-        <v>7085133</v>
+        <v>7084882</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11440,6 +11450,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11451,7 +11466,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>döda granar</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11469,10 +11484,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622714</v>
+        <v>123622666</v>
       </c>
       <c r="B96" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11481,38 +11496,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768493</v>
+        <v>768567</v>
       </c>
       <c r="R96" t="n">
-        <v>7085068</v>
+        <v>7085161</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11581,10 +11596,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622716</v>
+        <v>123622709</v>
       </c>
       <c r="B97" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11597,34 +11612,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768463</v>
+        <v>768616</v>
       </c>
       <c r="R97" t="n">
-        <v>7085126</v>
+        <v>7084853</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11677,11 +11692,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11698,7 +11708,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622665</v>
+        <v>123622711</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -11734,14 +11744,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768559</v>
+        <v>768579</v>
       </c>
       <c r="R98" t="n">
-        <v>7085175</v>
+        <v>7084911</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11810,7 +11820,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622706</v>
+        <v>123622735</v>
       </c>
       <c r="B99" t="n">
         <v>78788</v>
@@ -11846,14 +11856,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768635</v>
+        <v>768515</v>
       </c>
       <c r="R99" t="n">
-        <v>7084793</v>
+        <v>7085140</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11922,7 +11932,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622720</v>
+        <v>123622703</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -11958,14 +11968,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768441</v>
+        <v>768619</v>
       </c>
       <c r="R100" t="n">
-        <v>7085131</v>
+        <v>7084757</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12034,10 +12044,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622705</v>
+        <v>123622701</v>
       </c>
       <c r="B101" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12046,25 +12056,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12074,10 +12084,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768635</v>
+        <v>768642</v>
       </c>
       <c r="R101" t="n">
-        <v>7084792</v>
+        <v>7084688</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12130,11 +12140,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12151,10 +12156,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622730</v>
+        <v>123622704</v>
       </c>
       <c r="B102" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12167,37 +12172,51 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768457</v>
+        <v>768617</v>
       </c>
       <c r="R102" t="n">
-        <v>7085185</v>
+        <v>7084779</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12263,10 +12282,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622704</v>
+        <v>123622726</v>
       </c>
       <c r="B103" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12279,51 +12298,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768617</v>
+        <v>768378</v>
       </c>
       <c r="R103" t="n">
-        <v>7084779</v>
+        <v>7085228</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12389,10 +12394,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622733</v>
+        <v>123622702</v>
       </c>
       <c r="B104" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12401,38 +12406,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768511</v>
+        <v>768615</v>
       </c>
       <c r="R104" t="n">
-        <v>7085142</v>
+        <v>7084711</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12501,10 +12506,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622729</v>
+        <v>123622712</v>
       </c>
       <c r="B105" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12517,39 +12522,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768416</v>
+        <v>768522</v>
       </c>
       <c r="R105" t="n">
-        <v>7085204</v>
+        <v>7084946</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12594,11 +12594,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12607,11 +12602,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12628,10 +12618,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622713</v>
+        <v>123622733</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12640,38 +12630,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768497</v>
+        <v>768511</v>
       </c>
       <c r="R106" t="n">
-        <v>7085012</v>
+        <v>7085142</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12740,10 +12730,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622717</v>
+        <v>123622720</v>
       </c>
       <c r="B107" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12756,21 +12746,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12780,10 +12770,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768463</v>
+        <v>768441</v>
       </c>
       <c r="R107" t="n">
-        <v>7085126</v>
+        <v>7085131</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12836,11 +12826,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12857,7 +12842,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622723</v>
+        <v>123622665</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -12893,14 +12878,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768385</v>
+        <v>768559</v>
       </c>
       <c r="R108" t="n">
-        <v>7085111</v>
+        <v>7085175</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12969,10 +12954,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622703</v>
+        <v>123622729</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12985,34 +12970,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768619</v>
+        <v>768416</v>
       </c>
       <c r="R109" t="n">
-        <v>7084757</v>
+        <v>7085204</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13057,6 +13047,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13065,6 +13060,11 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13081,7 +13081,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622726</v>
+        <v>123622730</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -13121,10 +13121,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768378</v>
+        <v>768457</v>
       </c>
       <c r="R110" t="n">
-        <v>7085228</v>
+        <v>7085185</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13193,7 +13193,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622709</v>
+        <v>123622731</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -13229,14 +13229,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768616</v>
+        <v>768463</v>
       </c>
       <c r="R111" t="n">
-        <v>7084853</v>
+        <v>7085154</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13305,7 +13305,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622718</v>
+        <v>123622670</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -13341,14 +13341,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768450</v>
+        <v>768634</v>
       </c>
       <c r="R112" t="n">
-        <v>7085128</v>
+        <v>7084898</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13417,10 +13417,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622710</v>
+        <v>123622716</v>
       </c>
       <c r="B113" t="n">
-        <v>57491</v>
+        <v>79324</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13433,39 +13433,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1352</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768591</v>
+        <v>768463</v>
       </c>
       <c r="R113" t="n">
-        <v>7084882</v>
+        <v>7085126</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13510,11 +13505,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13526,7 +13516,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>döda granar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13544,10 +13534,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622715</v>
+        <v>123622705</v>
       </c>
       <c r="B114" t="n">
-        <v>78820</v>
+        <v>90955</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13556,38 +13546,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768491</v>
+        <v>768635</v>
       </c>
       <c r="R114" t="n">
-        <v>7085072</v>
+        <v>7084792</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13640,6 +13630,11 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13656,10 +13651,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622727</v>
+        <v>123622717</v>
       </c>
       <c r="B115" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13672,34 +13667,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768402</v>
+        <v>768463</v>
       </c>
       <c r="R115" t="n">
-        <v>7085218</v>
+        <v>7085126</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13752,6 +13747,11 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10003,7 +10003,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123622727</v>
+        <v>123622709</v>
       </c>
       <c r="B83" t="n">
         <v>78788</v>
@@ -10039,14 +10039,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768402</v>
+        <v>768616</v>
       </c>
       <c r="R83" t="n">
-        <v>7085218</v>
+        <v>7084853</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10115,7 +10115,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622732</v>
+        <v>123622731</v>
       </c>
       <c r="B84" t="n">
         <v>78788</v>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768481</v>
+        <v>768463</v>
       </c>
       <c r="R84" t="n">
-        <v>7085143</v>
+        <v>7085154</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622719</v>
+        <v>123622712</v>
       </c>
       <c r="B85" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10243,21 +10243,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768453</v>
+        <v>768522</v>
       </c>
       <c r="R85" t="n">
-        <v>7085131</v>
+        <v>7084946</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10323,11 +10323,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10344,10 +10339,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622715</v>
+        <v>123622670</v>
       </c>
       <c r="B86" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10360,34 +10355,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768491</v>
+        <v>768634</v>
       </c>
       <c r="R86" t="n">
-        <v>7085072</v>
+        <v>7084898</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10568,7 +10563,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622667</v>
+        <v>123622723</v>
       </c>
       <c r="B88" t="n">
         <v>78788</v>
@@ -10604,14 +10599,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768557</v>
+        <v>768385</v>
       </c>
       <c r="R88" t="n">
-        <v>7085109</v>
+        <v>7085111</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10680,7 +10675,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622714</v>
+        <v>123622667</v>
       </c>
       <c r="B89" t="n">
         <v>78788</v>
@@ -10716,14 +10711,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768493</v>
+        <v>768557</v>
       </c>
       <c r="R89" t="n">
-        <v>7085068</v>
+        <v>7085109</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10792,10 +10787,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622737</v>
+        <v>123622732</v>
       </c>
       <c r="B90" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10808,21 +10803,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10832,10 +10827,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768519</v>
+        <v>768481</v>
       </c>
       <c r="R90" t="n">
-        <v>7085133</v>
+        <v>7085143</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10888,11 +10883,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10909,7 +10899,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622723</v>
+        <v>123622665</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -10945,14 +10935,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768385</v>
+        <v>768559</v>
       </c>
       <c r="R91" t="n">
-        <v>7085111</v>
+        <v>7085175</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11021,10 +11011,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622725</v>
+        <v>123622705</v>
       </c>
       <c r="B92" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11033,38 +11023,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768375</v>
+        <v>768635</v>
       </c>
       <c r="R92" t="n">
-        <v>7085205</v>
+        <v>7084792</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11117,6 +11107,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11133,10 +11128,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622718</v>
+        <v>123622733</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11145,38 +11140,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768450</v>
+        <v>768511</v>
       </c>
       <c r="R93" t="n">
-        <v>7085128</v>
+        <v>7085142</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11245,7 +11240,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622713</v>
+        <v>123622735</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11281,14 +11276,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768497</v>
+        <v>768515</v>
       </c>
       <c r="R94" t="n">
-        <v>7085012</v>
+        <v>7085140</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11357,10 +11352,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622710</v>
+        <v>123622718</v>
       </c>
       <c r="B95" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11373,39 +11368,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768591</v>
+        <v>768450</v>
       </c>
       <c r="R95" t="n">
-        <v>7084882</v>
+        <v>7085128</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11450,11 +11440,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11463,11 +11448,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11484,10 +11464,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622666</v>
+        <v>123622701</v>
       </c>
       <c r="B96" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11496,38 +11476,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768567</v>
+        <v>768642</v>
       </c>
       <c r="R96" t="n">
-        <v>7085161</v>
+        <v>7084688</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11596,10 +11576,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622709</v>
+        <v>123622737</v>
       </c>
       <c r="B97" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11612,34 +11592,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768616</v>
+        <v>768519</v>
       </c>
       <c r="R97" t="n">
-        <v>7084853</v>
+        <v>7085133</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11692,6 +11672,11 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11708,10 +11693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622711</v>
+        <v>123622710</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11724,34 +11709,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768579</v>
+        <v>768591</v>
       </c>
       <c r="R98" t="n">
-        <v>7084911</v>
+        <v>7084882</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11796,6 +11786,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11804,6 +11799,11 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11820,10 +11820,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622735</v>
+        <v>123622716</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11836,34 +11836,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768515</v>
+        <v>768463</v>
       </c>
       <c r="R99" t="n">
-        <v>7085140</v>
+        <v>7085126</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11916,6 +11916,11 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11932,7 +11937,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622703</v>
+        <v>123622726</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -11968,14 +11973,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768619</v>
+        <v>768378</v>
       </c>
       <c r="R100" t="n">
-        <v>7084757</v>
+        <v>7085228</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12044,7 +12049,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622701</v>
+        <v>123622703</v>
       </c>
       <c r="B101" t="n">
         <v>78788</v>
@@ -12084,10 +12089,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768642</v>
+        <v>768619</v>
       </c>
       <c r="R101" t="n">
-        <v>7084688</v>
+        <v>7084757</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12156,10 +12161,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622704</v>
+        <v>123622702</v>
       </c>
       <c r="B102" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12172,51 +12177,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768617</v>
+        <v>768615</v>
       </c>
       <c r="R102" t="n">
-        <v>7084779</v>
+        <v>7084711</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12282,10 +12273,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622726</v>
+        <v>123622666</v>
       </c>
       <c r="B103" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12294,25 +12285,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12322,10 +12313,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768378</v>
+        <v>768567</v>
       </c>
       <c r="R103" t="n">
-        <v>7085228</v>
+        <v>7085161</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12394,7 +12385,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622702</v>
+        <v>123622730</v>
       </c>
       <c r="B104" t="n">
         <v>78788</v>
@@ -12430,14 +12421,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768615</v>
+        <v>768457</v>
       </c>
       <c r="R104" t="n">
-        <v>7084711</v>
+        <v>7085185</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12506,10 +12497,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622712</v>
+        <v>123622719</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12522,21 +12513,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12546,10 +12537,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768522</v>
+        <v>768453</v>
       </c>
       <c r="R105" t="n">
-        <v>7084946</v>
+        <v>7085131</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12602,6 +12593,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12618,10 +12614,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622733</v>
+        <v>123622704</v>
       </c>
       <c r="B106" t="n">
-        <v>78812</v>
+        <v>56692</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12630,41 +12626,55 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768511</v>
+        <v>768617</v>
       </c>
       <c r="R106" t="n">
-        <v>7085142</v>
+        <v>7084779</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12730,7 +12740,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622720</v>
+        <v>123622727</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -12766,14 +12776,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768441</v>
+        <v>768402</v>
       </c>
       <c r="R107" t="n">
-        <v>7085131</v>
+        <v>7085218</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12842,10 +12852,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622665</v>
+        <v>123622717</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12858,34 +12868,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768559</v>
+        <v>768463</v>
       </c>
       <c r="R108" t="n">
-        <v>7085175</v>
+        <v>7085126</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12938,6 +12948,11 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12954,10 +12969,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622729</v>
+        <v>123622720</v>
       </c>
       <c r="B109" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12970,39 +12985,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768416</v>
+        <v>768441</v>
       </c>
       <c r="R109" t="n">
-        <v>7085204</v>
+        <v>7085131</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13047,11 +13057,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13060,11 +13065,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13081,7 +13081,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622730</v>
+        <v>123622714</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -13117,14 +13117,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768457</v>
+        <v>768493</v>
       </c>
       <c r="R110" t="n">
-        <v>7085185</v>
+        <v>7085068</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13193,7 +13193,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622731</v>
+        <v>123622713</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -13229,14 +13229,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768463</v>
+        <v>768497</v>
       </c>
       <c r="R111" t="n">
-        <v>7085154</v>
+        <v>7085012</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13305,10 +13305,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622670</v>
+        <v>123622729</v>
       </c>
       <c r="B112" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13321,34 +13321,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768634</v>
+        <v>768416</v>
       </c>
       <c r="R112" t="n">
-        <v>7084898</v>
+        <v>7085204</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13393,6 +13398,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13401,6 +13411,11 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13417,10 +13432,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622716</v>
+        <v>123622725</v>
       </c>
       <c r="B113" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13433,34 +13448,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768463</v>
+        <v>768375</v>
       </c>
       <c r="R113" t="n">
-        <v>7085126</v>
+        <v>7085205</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13513,11 +13528,6 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13534,10 +13544,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622705</v>
+        <v>123622715</v>
       </c>
       <c r="B114" t="n">
-        <v>90955</v>
+        <v>78820</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13546,38 +13556,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768635</v>
+        <v>768491</v>
       </c>
       <c r="R114" t="n">
-        <v>7084792</v>
+        <v>7085072</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13630,11 +13640,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13651,10 +13656,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622717</v>
+        <v>123622711</v>
       </c>
       <c r="B115" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13667,34 +13672,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768463</v>
+        <v>768579</v>
       </c>
       <c r="R115" t="n">
-        <v>7085126</v>
+        <v>7084911</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13747,11 +13752,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10003,7 +10003,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123622709</v>
+        <v>123622706</v>
       </c>
       <c r="B83" t="n">
         <v>78788</v>
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>768616</v>
+        <v>768635</v>
       </c>
       <c r="R83" t="n">
-        <v>7084853</v>
+        <v>7084793</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10115,7 +10115,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622731</v>
+        <v>123622718</v>
       </c>
       <c r="B84" t="n">
         <v>78788</v>
@@ -10151,14 +10151,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768463</v>
+        <v>768450</v>
       </c>
       <c r="R84" t="n">
-        <v>7085154</v>
+        <v>7085128</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622712</v>
+        <v>123622723</v>
       </c>
       <c r="B85" t="n">
         <v>78788</v>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768522</v>
+        <v>768385</v>
       </c>
       <c r="R85" t="n">
-        <v>7084946</v>
+        <v>7085111</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10339,7 +10339,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622670</v>
+        <v>123622726</v>
       </c>
       <c r="B86" t="n">
         <v>78788</v>
@@ -10375,14 +10375,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768634</v>
+        <v>768378</v>
       </c>
       <c r="R86" t="n">
-        <v>7084898</v>
+        <v>7085228</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10451,10 +10451,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622706</v>
+        <v>123622715</v>
       </c>
       <c r="B87" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10467,34 +10467,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768635</v>
+        <v>768491</v>
       </c>
       <c r="R87" t="n">
-        <v>7084793</v>
+        <v>7085072</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622723</v>
+        <v>123622720</v>
       </c>
       <c r="B88" t="n">
         <v>78788</v>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768385</v>
+        <v>768441</v>
       </c>
       <c r="R88" t="n">
-        <v>7085111</v>
+        <v>7085131</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10675,10 +10675,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622667</v>
+        <v>123622717</v>
       </c>
       <c r="B89" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10691,34 +10691,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768557</v>
+        <v>768463</v>
       </c>
       <c r="R89" t="n">
-        <v>7085109</v>
+        <v>7085126</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10771,6 +10771,11 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10787,10 +10792,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622732</v>
+        <v>123622704</v>
       </c>
       <c r="B90" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10803,37 +10808,51 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768481</v>
+        <v>768617</v>
       </c>
       <c r="R90" t="n">
-        <v>7085143</v>
+        <v>7084779</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10899,7 +10918,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622665</v>
+        <v>123622711</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -10935,14 +10954,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768559</v>
+        <v>768579</v>
       </c>
       <c r="R91" t="n">
-        <v>7085175</v>
+        <v>7084911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11011,10 +11030,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622705</v>
+        <v>123622733</v>
       </c>
       <c r="B92" t="n">
-        <v>90955</v>
+        <v>78812</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11027,34 +11046,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768635</v>
+        <v>768511</v>
       </c>
       <c r="R92" t="n">
-        <v>7084792</v>
+        <v>7085142</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11107,11 +11126,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11128,10 +11142,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622733</v>
+        <v>123622727</v>
       </c>
       <c r="B93" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11140,25 +11154,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11168,10 +11182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768511</v>
+        <v>768402</v>
       </c>
       <c r="R93" t="n">
-        <v>7085142</v>
+        <v>7085218</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11240,7 +11254,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622735</v>
+        <v>123622703</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11276,14 +11290,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768515</v>
+        <v>768619</v>
       </c>
       <c r="R94" t="n">
-        <v>7085140</v>
+        <v>7084757</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11366,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622718</v>
+        <v>123622712</v>
       </c>
       <c r="B95" t="n">
         <v>78788</v>
@@ -11392,10 +11406,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768450</v>
+        <v>768522</v>
       </c>
       <c r="R95" t="n">
-        <v>7085128</v>
+        <v>7084946</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11464,10 +11478,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622701</v>
+        <v>123622716</v>
       </c>
       <c r="B96" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11480,34 +11494,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768642</v>
+        <v>768463</v>
       </c>
       <c r="R96" t="n">
-        <v>7084688</v>
+        <v>7085126</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11560,6 +11574,11 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11576,10 +11595,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622737</v>
+        <v>123622729</v>
       </c>
       <c r="B97" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11592,34 +11611,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768519</v>
+        <v>768416</v>
       </c>
       <c r="R97" t="n">
-        <v>7085133</v>
+        <v>7085204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11664,6 +11688,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11675,7 +11704,7 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>döda granar</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11693,10 +11722,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622710</v>
+        <v>123622666</v>
       </c>
       <c r="B98" t="n">
-        <v>57491</v>
+        <v>78812</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11705,43 +11734,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768591</v>
+        <v>768567</v>
       </c>
       <c r="R98" t="n">
-        <v>7084882</v>
+        <v>7085161</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11786,11 +11810,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11799,11 +11818,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11820,10 +11834,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622716</v>
+        <v>123622709</v>
       </c>
       <c r="B99" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11836,34 +11850,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768463</v>
+        <v>768616</v>
       </c>
       <c r="R99" t="n">
-        <v>7085126</v>
+        <v>7084853</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11916,11 +11930,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11937,7 +11946,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622726</v>
+        <v>123622667</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -11977,10 +11986,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768378</v>
+        <v>768557</v>
       </c>
       <c r="R100" t="n">
-        <v>7085228</v>
+        <v>7085109</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12049,10 +12058,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622703</v>
+        <v>123622719</v>
       </c>
       <c r="B101" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12065,34 +12074,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768619</v>
+        <v>768453</v>
       </c>
       <c r="R101" t="n">
-        <v>7084757</v>
+        <v>7085131</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12145,6 +12154,11 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12161,10 +12175,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622702</v>
+        <v>123622737</v>
       </c>
       <c r="B102" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12177,34 +12191,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768615</v>
+        <v>768519</v>
       </c>
       <c r="R102" t="n">
-        <v>7084711</v>
+        <v>7085133</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12257,6 +12271,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12273,10 +12292,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622666</v>
+        <v>123622725</v>
       </c>
       <c r="B103" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12285,25 +12304,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12313,10 +12332,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768567</v>
+        <v>768375</v>
       </c>
       <c r="R103" t="n">
-        <v>7085161</v>
+        <v>7085205</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12385,7 +12404,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622730</v>
+        <v>123622670</v>
       </c>
       <c r="B104" t="n">
         <v>78788</v>
@@ -12421,14 +12440,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768457</v>
+        <v>768634</v>
       </c>
       <c r="R104" t="n">
-        <v>7085185</v>
+        <v>7084898</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12497,10 +12516,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622719</v>
+        <v>123622710</v>
       </c>
       <c r="B105" t="n">
-        <v>79324</v>
+        <v>57491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12513,34 +12532,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1352</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768453</v>
+        <v>768591</v>
       </c>
       <c r="R105" t="n">
-        <v>7085131</v>
+        <v>7084882</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12585,6 +12609,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12596,7 +12625,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>döda granar</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12614,10 +12643,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622704</v>
+        <v>123622701</v>
       </c>
       <c r="B106" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12630,51 +12659,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768617</v>
+        <v>768642</v>
       </c>
       <c r="R106" t="n">
-        <v>7084779</v>
+        <v>7084688</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12740,10 +12755,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622727</v>
+        <v>123622705</v>
       </c>
       <c r="B107" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12752,38 +12767,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768402</v>
+        <v>768635</v>
       </c>
       <c r="R107" t="n">
-        <v>7085218</v>
+        <v>7084792</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12836,6 +12851,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12852,10 +12872,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622717</v>
+        <v>123622713</v>
       </c>
       <c r="B108" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12868,21 +12888,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12892,10 +12912,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768463</v>
+        <v>768497</v>
       </c>
       <c r="R108" t="n">
-        <v>7085126</v>
+        <v>7085012</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12948,11 +12968,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12969,7 +12984,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622720</v>
+        <v>123622731</v>
       </c>
       <c r="B109" t="n">
         <v>78788</v>
@@ -13005,14 +13020,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768441</v>
+        <v>768463</v>
       </c>
       <c r="R109" t="n">
-        <v>7085131</v>
+        <v>7085154</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13081,7 +13096,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622714</v>
+        <v>123622665</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -13117,14 +13132,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768493</v>
+        <v>768559</v>
       </c>
       <c r="R110" t="n">
-        <v>7085068</v>
+        <v>7085175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13193,7 +13208,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622713</v>
+        <v>123622714</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -13233,10 +13248,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768497</v>
+        <v>768493</v>
       </c>
       <c r="R111" t="n">
-        <v>7085012</v>
+        <v>7085068</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13305,10 +13320,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622729</v>
+        <v>123622702</v>
       </c>
       <c r="B112" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13321,39 +13336,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768416</v>
+        <v>768615</v>
       </c>
       <c r="R112" t="n">
-        <v>7085204</v>
+        <v>7084711</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13398,11 +13408,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13411,11 +13416,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13432,7 +13432,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622725</v>
+        <v>123622730</v>
       </c>
       <c r="B113" t="n">
         <v>78788</v>
@@ -13472,10 +13472,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768375</v>
+        <v>768457</v>
       </c>
       <c r="R113" t="n">
-        <v>7085205</v>
+        <v>7085185</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13544,10 +13544,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622715</v>
+        <v>123622735</v>
       </c>
       <c r="B114" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13560,34 +13560,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768491</v>
+        <v>768515</v>
       </c>
       <c r="R114" t="n">
-        <v>7085072</v>
+        <v>7085140</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622711</v>
+        <v>123622732</v>
       </c>
       <c r="B115" t="n">
         <v>78788</v>
@@ -13692,14 +13692,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768579</v>
+        <v>768481</v>
       </c>
       <c r="R115" t="n">
-        <v>7084911</v>
+        <v>7085143</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10563,10 +10563,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622720</v>
+        <v>123622704</v>
       </c>
       <c r="B88" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10579,37 +10579,51 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768441</v>
+        <v>768617</v>
       </c>
       <c r="R88" t="n">
-        <v>7085131</v>
+        <v>7084779</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10675,10 +10689,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622717</v>
+        <v>123622720</v>
       </c>
       <c r="B89" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10691,21 +10705,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10715,10 +10729,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768463</v>
+        <v>768441</v>
       </c>
       <c r="R89" t="n">
-        <v>7085126</v>
+        <v>7085131</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10771,11 +10785,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10792,10 +10801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622704</v>
+        <v>123622717</v>
       </c>
       <c r="B90" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10808,51 +10817,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768617</v>
+        <v>768463</v>
       </c>
       <c r="R90" t="n">
-        <v>7084779</v>
+        <v>7085126</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10902,6 +10897,11 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -10003,10 +10003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123622706</v>
+        <v>123622705</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10015,25 +10015,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
         <v>768635</v>
       </c>
       <c r="R83" t="n">
-        <v>7084793</v>
+        <v>7084792</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10099,6 +10099,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>grangrenar död gran</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10115,10 +10120,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123622718</v>
+        <v>123622716</v>
       </c>
       <c r="B84" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10131,21 +10136,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10155,10 +10160,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>768450</v>
+        <v>768463</v>
       </c>
       <c r="R84" t="n">
-        <v>7085128</v>
+        <v>7085126</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10211,6 +10216,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10227,7 +10237,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123622723</v>
+        <v>123622709</v>
       </c>
       <c r="B85" t="n">
         <v>78788</v>
@@ -10263,14 +10273,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>768385</v>
+        <v>768616</v>
       </c>
       <c r="R85" t="n">
-        <v>7085111</v>
+        <v>7084853</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10339,7 +10349,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123622726</v>
+        <v>123622731</v>
       </c>
       <c r="B86" t="n">
         <v>78788</v>
@@ -10379,10 +10389,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>768378</v>
+        <v>768463</v>
       </c>
       <c r="R86" t="n">
-        <v>7085228</v>
+        <v>7085154</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10451,10 +10461,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123622715</v>
+        <v>123622704</v>
       </c>
       <c r="B87" t="n">
-        <v>78820</v>
+        <v>56692</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10467,37 +10477,51 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>768491</v>
+        <v>768617</v>
       </c>
       <c r="R87" t="n">
-        <v>7085072</v>
+        <v>7084779</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10563,10 +10587,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123622704</v>
+        <v>123622715</v>
       </c>
       <c r="B88" t="n">
-        <v>56692</v>
+        <v>78820</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10579,51 +10603,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>768617</v>
+        <v>768491</v>
       </c>
       <c r="R88" t="n">
-        <v>7084779</v>
+        <v>7085072</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10689,7 +10699,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123622720</v>
+        <v>123622718</v>
       </c>
       <c r="B89" t="n">
         <v>78788</v>
@@ -10729,10 +10739,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>768441</v>
+        <v>768450</v>
       </c>
       <c r="R89" t="n">
-        <v>7085131</v>
+        <v>7085128</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10801,10 +10811,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123622717</v>
+        <v>123622711</v>
       </c>
       <c r="B90" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10817,34 +10827,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>768463</v>
+        <v>768579</v>
       </c>
       <c r="R90" t="n">
-        <v>7085126</v>
+        <v>7084911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10897,11 +10907,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10918,10 +10923,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123622711</v>
+        <v>123622717</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10934,34 +10939,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>768579</v>
+        <v>768463</v>
       </c>
       <c r="R91" t="n">
-        <v>7084911</v>
+        <v>7085126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11014,6 +11019,11 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11030,10 +11040,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123622733</v>
+        <v>123622737</v>
       </c>
       <c r="B92" t="n">
-        <v>78812</v>
+        <v>79869</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11042,25 +11052,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11070,10 +11080,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>768511</v>
+        <v>768519</v>
       </c>
       <c r="R92" t="n">
-        <v>7085142</v>
+        <v>7085133</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11126,6 +11136,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11142,7 +11157,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123622727</v>
+        <v>123622732</v>
       </c>
       <c r="B93" t="n">
         <v>78788</v>
@@ -11182,10 +11197,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>768402</v>
+        <v>768481</v>
       </c>
       <c r="R93" t="n">
-        <v>7085218</v>
+        <v>7085143</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11254,7 +11269,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123622703</v>
+        <v>123622701</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11294,10 +11309,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>768619</v>
+        <v>768642</v>
       </c>
       <c r="R94" t="n">
-        <v>7084757</v>
+        <v>7084688</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11366,10 +11381,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123622712</v>
+        <v>123622733</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11378,38 +11393,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>768522</v>
+        <v>768511</v>
       </c>
       <c r="R95" t="n">
-        <v>7084946</v>
+        <v>7085142</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11478,10 +11493,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123622716</v>
+        <v>123622720</v>
       </c>
       <c r="B96" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11494,21 +11509,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11518,10 +11533,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>768463</v>
+        <v>768441</v>
       </c>
       <c r="R96" t="n">
-        <v>7085126</v>
+        <v>7085131</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11574,11 +11589,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11595,10 +11605,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123622729</v>
+        <v>123622703</v>
       </c>
       <c r="B97" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11611,39 +11621,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>768416</v>
+        <v>768619</v>
       </c>
       <c r="R97" t="n">
-        <v>7085204</v>
+        <v>7084757</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11688,11 +11693,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11701,11 +11701,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11722,10 +11717,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123622666</v>
+        <v>123622665</v>
       </c>
       <c r="B98" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11734,25 +11729,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11762,10 +11757,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>768567</v>
+        <v>768559</v>
       </c>
       <c r="R98" t="n">
-        <v>7085161</v>
+        <v>7085175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11834,7 +11829,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123622709</v>
+        <v>123622735</v>
       </c>
       <c r="B99" t="n">
         <v>78788</v>
@@ -11870,14 +11865,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>768616</v>
+        <v>768515</v>
       </c>
       <c r="R99" t="n">
-        <v>7084853</v>
+        <v>7085140</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11946,7 +11941,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123622667</v>
+        <v>123622712</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -11982,14 +11977,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>768557</v>
+        <v>768522</v>
       </c>
       <c r="R100" t="n">
-        <v>7085109</v>
+        <v>7084946</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12058,10 +12053,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123622719</v>
+        <v>123622725</v>
       </c>
       <c r="B101" t="n">
-        <v>79324</v>
+        <v>78788</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12074,34 +12069,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>768453</v>
+        <v>768375</v>
       </c>
       <c r="R101" t="n">
-        <v>7085131</v>
+        <v>7085205</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12154,11 +12149,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12175,10 +12165,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123622737</v>
+        <v>123622667</v>
       </c>
       <c r="B102" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12191,21 +12181,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12215,10 +12205,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>768519</v>
+        <v>768557</v>
       </c>
       <c r="R102" t="n">
-        <v>7085133</v>
+        <v>7085109</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12271,11 +12261,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12292,7 +12277,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123622725</v>
+        <v>123622702</v>
       </c>
       <c r="B103" t="n">
         <v>78788</v>
@@ -12328,14 +12313,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>768375</v>
+        <v>768615</v>
       </c>
       <c r="R103" t="n">
-        <v>7085205</v>
+        <v>7084711</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12404,10 +12389,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123622670</v>
+        <v>123622666</v>
       </c>
       <c r="B104" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12416,38 +12401,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>768634</v>
+        <v>768567</v>
       </c>
       <c r="R104" t="n">
-        <v>7084898</v>
+        <v>7085161</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12516,10 +12501,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123622710</v>
+        <v>123622713</v>
       </c>
       <c r="B105" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12532,39 +12517,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>768591</v>
+        <v>768497</v>
       </c>
       <c r="R105" t="n">
-        <v>7084882</v>
+        <v>7085012</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12609,11 +12589,6 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>barkfläk</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12622,11 +12597,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>döda granar</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12643,10 +12613,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123622701</v>
+        <v>123622710</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12659,34 +12629,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>768642</v>
+        <v>768591</v>
       </c>
       <c r="R106" t="n">
-        <v>7084688</v>
+        <v>7084882</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12731,6 +12706,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12739,6 +12719,11 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12755,10 +12740,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123622705</v>
+        <v>123622670</v>
       </c>
       <c r="B107" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12767,25 +12752,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12795,10 +12780,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>768635</v>
+        <v>768634</v>
       </c>
       <c r="R107" t="n">
-        <v>7084792</v>
+        <v>7084898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12851,11 +12836,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>grangrenar död gran</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12872,7 +12852,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123622713</v>
+        <v>123622730</v>
       </c>
       <c r="B108" t="n">
         <v>78788</v>
@@ -12908,14 +12888,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>768497</v>
+        <v>768457</v>
       </c>
       <c r="R108" t="n">
-        <v>7085012</v>
+        <v>7085185</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12984,7 +12964,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123622731</v>
+        <v>123622723</v>
       </c>
       <c r="B109" t="n">
         <v>78788</v>
@@ -13020,14 +13000,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>768463</v>
+        <v>768385</v>
       </c>
       <c r="R109" t="n">
-        <v>7085154</v>
+        <v>7085111</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13096,7 +13076,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123622665</v>
+        <v>123622714</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -13132,14 +13112,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>768559</v>
+        <v>768493</v>
       </c>
       <c r="R110" t="n">
-        <v>7085175</v>
+        <v>7085068</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13208,10 +13188,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123622714</v>
+        <v>123622729</v>
       </c>
       <c r="B111" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13224,34 +13204,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>SO Stubbmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>768493</v>
+        <v>768416</v>
       </c>
       <c r="R111" t="n">
-        <v>7085068</v>
+        <v>7085204</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13296,6 +13281,11 @@
           <t>10:15</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>barkfläk</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13304,6 +13294,11 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>döda granar</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13320,7 +13315,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123622702</v>
+        <v>123622727</v>
       </c>
       <c r="B112" t="n">
         <v>78788</v>
@@ -13356,14 +13351,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>V Spångmyran, Ultervik, Vb</t>
+          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>768615</v>
+        <v>768402</v>
       </c>
       <c r="R112" t="n">
-        <v>7084711</v>
+        <v>7085218</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13432,7 +13427,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123622730</v>
+        <v>123622726</v>
       </c>
       <c r="B113" t="n">
         <v>78788</v>
@@ -13472,10 +13467,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>768457</v>
+        <v>768378</v>
       </c>
       <c r="R113" t="n">
-        <v>7085185</v>
+        <v>7085228</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13544,10 +13539,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123622735</v>
+        <v>123622719</v>
       </c>
       <c r="B114" t="n">
-        <v>78788</v>
+        <v>79324</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13560,34 +13555,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>SO Stubbmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>768515</v>
+        <v>768453</v>
       </c>
       <c r="R114" t="n">
-        <v>7085140</v>
+        <v>7085131</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13640,6 +13635,11 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13656,7 +13656,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123622732</v>
+        <v>123622706</v>
       </c>
       <c r="B115" t="n">
         <v>78788</v>
@@ -13692,14 +13692,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stubbmyrberget, S Ulterviksvägen, Ultervik, Vb</t>
+          <t>V Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>768481</v>
+        <v>768635</v>
       </c>
       <c r="R115" t="n">
-        <v>7085143</v>
+        <v>7084793</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13766,6 +13766,107 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>125960229</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Degersjö, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>768650</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7084967</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13771,7 +13771,7 @@
         <v>125960229</v>
       </c>
       <c r="B116" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13771,7 +13771,7 @@
         <v>125960229</v>
       </c>
       <c r="B116" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13771,7 +13771,7 @@
         <v>125960229</v>
       </c>
       <c r="B116" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13771,7 +13771,7 @@
         <v>125960229</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13771,7 +13771,7 @@
         <v>125960229</v>
       </c>
       <c r="B116" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13872,7 +13872,7 @@
         <v>126708529</v>
       </c>
       <c r="B117" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>126708528</v>
       </c>
       <c r="B118" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>126708538</v>
       </c>
       <c r="B119" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13872,7 +13872,7 @@
         <v>126708529</v>
       </c>
       <c r="B117" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>126708528</v>
       </c>
       <c r="B118" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>126708538</v>
       </c>
       <c r="B119" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 52244-2024 artfynd.xlsx
+++ b/artfynd/A 52244-2024 artfynd.xlsx
@@ -13872,7 +13872,7 @@
         <v>126708529</v>
       </c>
       <c r="B117" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>126708528</v>
       </c>
       <c r="B118" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>126708538</v>
       </c>
       <c r="B119" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
